--- a/template/Jev_Close_Template.xlsx
+++ b/template/Jev_Close_Template.xlsx
@@ -18,23 +18,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Ent" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Params" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Months" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Monthly" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Lists" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_UseCase" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_InferenceAcc" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Cohort" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_EarlierCohorts" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Signups" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Contracts" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_EntMonth" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Pipeline" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Concentration" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Checks" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Reliability" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Hourly" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_FcHistory" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overrides" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Params" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Months" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Monthly" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Lists" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_UseCase" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_InferenceAcc" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Cohort" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_EarlierCohorts" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Signups" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Contracts" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_EntMonth" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Pipeline" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Concentration" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Checks" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Reliability" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Hourly" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_FcHistory" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,16 +46,16 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="14">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="mmm yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0);-"/>
-    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);-"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00;(#,##0.00);-"/>
-    <numFmt numFmtId="169" formatCode="0.0%;(0.0%);-"/>
-    <numFmt numFmtId="170" formatCode="$#,##0.0000;($#,##0.0000);-"/>
-    <numFmt numFmtId="171" formatCode="#,##0.000;(#,##0.000);-"/>
-    <numFmt numFmtId="172" formatCode="$#,##0;($#,##0);-"/>
-    <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);0"/>
-    <numFmt numFmtId="174" formatCode="$#,##0.00;($#,##0.00);-"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00;($#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);-"/>
+    <numFmt numFmtId="168" formatCode="#,##0;(#,##0);-"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00;(#,##0.00);-"/>
+    <numFmt numFmtId="170" formatCode="0.0%;(0.0%);-"/>
+    <numFmt numFmtId="171" formatCode="$#,##0.0000;($#,##0.0000);-"/>
+    <numFmt numFmtId="172" formatCode="#,##0.000;(#,##0.000);-"/>
+    <numFmt numFmtId="173" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00);0"/>
     <numFmt numFmtId="175" formatCode="0.000000"/>
     <numFmt numFmtId="176" formatCode="0.00&quot;x&quot;;(0.00&quot;x&quot;);-"/>
     <numFmt numFmtId="177" formatCode="0%;[Red](0%);-"/>
@@ -96,8 +97,9 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00008000"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -106,12 +108,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="11"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -125,17 +126,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF5"/>
+        <fgColor rgb="00F3F6FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F6FA"/>
+        <fgColor rgb="00E8EEF5"/>
       </patternFill>
     </fill>
     <fill>
@@ -156,62 +162,75 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="175" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -611,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -649,109 +668,127 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>3. Blue cells are judgment inputs (forecast and capacity). The runner seeds them from config.yaml; edit them here to test scenarios.</t>
+          <t>3. Judgment inputs (forecast and capacity) live on the Overrides tab, seeded from config.yaml. Type an override in a yellow cell to test a scenario.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Bad entries are ignored, not fatal: a word, an error or an out-of-range number falls back to the model value. Set the switch on Overrides to OFF to undo every override at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>4. Grey-shaded cells on Checks and Summary are for people and the agent: owners, explanations, commentary.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>This close</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>As-of month</t>
-        </is>
-      </c>
-      <c r="B10" s="4">
-        <f>Data_Params!$B$2</f>
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Generated</t>
-        </is>
-      </c>
-      <c r="B11" s="5">
-        <f>Data_Params!$B$13</f>
+          <t>As-of month</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>Data_Params!$B$2</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Usage grain</t>
+          <t>Generated</t>
         </is>
       </c>
       <c r="B12" s="5">
-        <f>Data_Params!$B$9</f>
+        <f>Data_Params!$B$13</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Sources connected</t>
+          <t>Usage grain</t>
         </is>
       </c>
       <c r="B13" s="5">
-        <f>Data_Params!$B$12</f>
+        <f>Data_Params!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Usage data from</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <f>Data_Params!$B$10</f>
+          <t>Sources connected</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>Data_Params!$B$12</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Usage data to</t>
+          <t>Usage data from</t>
         </is>
       </c>
       <c r="B15" s="6">
-        <f>Data_Params!$B$11</f>
+        <f>Data_Params!$B$10</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Usage data to</t>
+        </is>
+      </c>
+      <c r="B16" s="6">
+        <f>Data_Params!$B$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Checks flagged</t>
         </is>
       </c>
-      <c r="B16" s="5">
+      <c r="B17" s="5">
         <f>COUNTIF(Checks!$G$5:$G$154,"FLAG")</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Overrides</t>
+        </is>
+      </c>
+      <c r="B18" s="5">
+        <f>Overrides!$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Color key: blue = input, black = formula, green = link to another tab, yellow = key assumption, grey tab = data.</t>
         </is>
@@ -818,15 +855,15 @@
           <t>Forecast month</t>
         </is>
       </c>
-      <c r="B5" s="44">
+      <c r="B5" s="42">
         <f>EDATE(Data_Params!$B$2,1)</f>
         <v/>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="42">
         <f>EDATE(Data_Params!$B$2,2)</f>
         <v/>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="42">
         <f>EDATE(Data_Params!$B$2,3)</f>
         <v/>
       </c>
@@ -902,7 +939,7 @@
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>Data_Params!$B$4</f>
+        <f>Overrides!$E$22</f>
         <v/>
       </c>
     </row>
@@ -4152,39 +4189,39 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="K53" s="43">
+      <c r="K53" s="41">
         <f>SUM(K13:K52)</f>
         <v/>
       </c>
-      <c r="L53" s="43">
+      <c r="L53" s="41">
         <f>SUM(L13:L52)</f>
         <v/>
       </c>
-      <c r="M53" s="43">
+      <c r="M53" s="41">
         <f>SUM(M13:M52)</f>
         <v/>
       </c>
-      <c r="N53" s="43">
+      <c r="N53" s="41">
         <f>SUM(N13:N52)</f>
         <v/>
       </c>
-      <c r="O53" s="43">
+      <c r="O53" s="41">
         <f>SUM(O13:O52)</f>
         <v/>
       </c>
-      <c r="P53" s="43">
+      <c r="P53" s="41">
         <f>SUM(P13:P52)</f>
         <v/>
       </c>
-      <c r="Q53" s="43">
+      <c r="Q53" s="41">
         <f>SUM(Q13:Q52)</f>
         <v/>
       </c>
-      <c r="R53" s="43">
+      <c r="R53" s="41">
         <f>SUM(R13:R52)</f>
         <v/>
       </c>
-      <c r="S53" s="43">
+      <c r="S53" s="41">
         <f>SUM(S13:S52)</f>
         <v/>
       </c>
@@ -9024,7 +9061,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Value (set on Overrides)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -9039,8 +9076,9 @@
           <t>Tokens per second per busy GPU</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n">
-        <v>20604</v>
+      <c r="B6" s="43">
+        <f>Overrides!$E$23</f>
+        <v/>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -9054,8 +9092,9 @@
           <t>Target utilization at peak</t>
         </is>
       </c>
-      <c r="B7" s="38" t="n">
-        <v>0.85</v>
+      <c r="B7" s="37">
+        <f>Overrides!$E$24</f>
+        <v/>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -9069,8 +9108,9 @@
           <t>Reserved rate ($ / GPU-hour)</t>
         </is>
       </c>
-      <c r="B8" s="46" t="n">
-        <v>2.5</v>
+      <c r="B8" s="14">
+        <f>Overrides!$E$25</f>
+        <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -9084,8 +9124,9 @@
           <t>On-demand rate ($ / GPU-hour)</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n">
-        <v>3</v>
+      <c r="B9" s="14">
+        <f>Overrides!$E$26</f>
+        <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -9099,8 +9140,9 @@
           <t>Peak hour / average (override if no hourly data)</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
-        <v>1.75</v>
+      <c r="B10" s="34">
+        <f>Overrides!$E$27</f>
+        <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -9114,8 +9156,9 @@
           <t>Quietest hour / average (override if no hourly data)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
-        <v>0.55</v>
+      <c r="B11" s="34">
+        <f>Overrides!$E$28</f>
+        <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -9129,7 +9172,7 @@
           <t>Peak hour / average (used)</t>
         </is>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="38">
         <f>IF(COUNT(Data_Hourly!$B$2:$B$169)=0,B10,MAX(Data_Hourly!$B$2:$B$169)/AVERAGE(Data_Hourly!$B$2:$B$169))</f>
         <v/>
       </c>
@@ -9145,7 +9188,7 @@
           <t>Quietest hour / average (used)</t>
         </is>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="38">
         <f>IF(COUNT(Data_Hourly!$B$2:$B$169)=0,B11,MIN(Data_Hourly!$B$2:$B$169)/AVERAGE(Data_Hourly!$B$2:$B$169))</f>
         <v/>
       </c>
@@ -9219,39 +9262,39 @@
           <t>Tokens per day (B)</t>
         </is>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="39">
         <f>Forecast!B127</f>
         <v/>
       </c>
-      <c r="C18" s="41">
+      <c r="C18" s="39">
         <f>Forecast!C127</f>
         <v/>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="39">
         <f>Forecast!D127</f>
         <v/>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="39">
         <f>Forecast!E127</f>
         <v/>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="39">
         <f>Forecast!F127</f>
         <v/>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="39">
         <f>Forecast!G127</f>
         <v/>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="39">
         <f>Forecast!H127</f>
         <v/>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="39">
         <f>Forecast!I127</f>
         <v/>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="39">
         <f>Forecast!J127</f>
         <v/>
       </c>
@@ -9391,39 +9434,39 @@
           <t>GPUs at peak</t>
         </is>
       </c>
-      <c r="B22" s="47">
+      <c r="B22" s="44">
         <f>ROUNDUP(B20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="44">
         <f>ROUNDUP(C20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="44">
         <f>ROUNDUP(D20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="44">
         <f>ROUNDUP(E20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="44">
         <f>ROUNDUP(F20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="G22" s="47">
+      <c r="G22" s="44">
         <f>ROUNDUP(G20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="H22" s="47">
+      <c r="H22" s="44">
         <f>ROUNDUP(H20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="I22" s="47">
+      <c r="I22" s="44">
         <f>ROUNDUP(I20/$B$6/$B$7,0)</f>
         <v/>
       </c>
-      <c r="J22" s="47">
+      <c r="J22" s="44">
         <f>ROUNDUP(J20/$B$6/$B$7,0)</f>
         <v/>
       </c>
@@ -9434,45 +9477,45 @@
           <t>GPUs for base load</t>
         </is>
       </c>
-      <c r="B23" s="47">
+      <c r="B23" s="44">
         <f>ROUNDDOWN(B21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="C23" s="47">
+      <c r="C23" s="44">
         <f>ROUNDDOWN(C21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="D23" s="47">
+      <c r="D23" s="44">
         <f>ROUNDDOWN(D21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="44">
         <f>ROUNDDOWN(E21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="F23" s="47">
+      <c r="F23" s="44">
         <f>ROUNDDOWN(F21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="G23" s="47">
+      <c r="G23" s="44">
         <f>ROUNDDOWN(G21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="H23" s="47">
+      <c r="H23" s="44">
         <f>ROUNDDOWN(H21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="44">
         <f>ROUNDDOWN(I21/$B$6,0)</f>
         <v/>
       </c>
-      <c r="J23" s="47">
+      <c r="J23" s="44">
         <f>ROUNDDOWN(J21/$B$6,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
@@ -9484,7 +9527,7 @@
           <t>Reserve: base-load GPUs in the LOW case, next month (capacity that stays busy)</t>
         </is>
       </c>
-      <c r="B27" s="47">
+      <c r="B27" s="44">
         <f>B23</f>
         <v/>
       </c>
@@ -9495,7 +9538,7 @@
           <t>Base case peak on top of that, rented on demand</t>
         </is>
       </c>
-      <c r="B28" s="47">
+      <c r="B28" s="44">
         <f>MAX(0,E22-$B$27)</f>
         <v/>
       </c>
@@ -9506,7 +9549,7 @@
           <t>High case peak: on-demand headroom to line up with the provider</t>
         </is>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="44">
         <f>MAX(0,H22-$B$27)</f>
         <v/>
       </c>
@@ -9639,15 +9682,15 @@
           <t>Serving gross margin, recommended strategy</t>
         </is>
       </c>
-      <c r="B37" s="48">
+      <c r="B37" s="45">
         <f>IF(OR(NOT(ISNUMBER(B33)),B36=0),"",1-B33/B36)</f>
         <v/>
       </c>
-      <c r="C37" s="48">
+      <c r="C37" s="45">
         <f>IF(OR(NOT(ISNUMBER(C33)),C36=0),"",1-C33/C36)</f>
         <v/>
       </c>
-      <c r="D37" s="48">
+      <c r="D37" s="45">
         <f>IF(OR(NOT(ISNUMBER(D33)),D36=0),"",1-D33/D36)</f>
         <v/>
       </c>
@@ -9665,6 +9708,1486 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00E69138"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1">
+        <f>Data_Params!$B$14&amp;" | Overrides: change a number without touching the data"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Type in the yellow cells only. Every override is checked: a blank, a word, an error or a value outside the allowed range is ignored and the model value is used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Master switch</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>ON = use the overrides and adjustments below. OFF = every tab goes back to the model values; nothing typed here is lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Active now</t>
+        </is>
+      </c>
+      <c r="C5" s="2">
+        <f>IF(Overrides!$C$4&lt;&gt;"ON","Switch is OFF: model values everywhere",COUNTIF($F$8:$F$39,"Applied")&amp;" input(s) and "&amp;COUNTIF($H$46:$H$75,"Applied")&amp;" adjustment(s) applied")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Model value</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Used</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Allowed range</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Why / who / date</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>tail_factor.low</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Cohort development factor beyond observed history, low</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="D8" s="48" t="n"/>
+      <c r="E8" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D8),D8&gt;=0.5,D8&lt;=1.5),D8,C8),C8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="3">
+        <f>IFERROR(IF(ISBLANK(D8),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D8),"Ignored: error value",IF(NOT(ISNUMBER(D8)),"Ignored: not a number",IF(OR(D8&lt;0.5,D8&gt;1.5),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>0.5 to 1.5</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>tail_factor.base</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Cohort development factor beyond observed history, base</t>
+        </is>
+      </c>
+      <c r="C9" s="47" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D9),D9&gt;=0.5,D9&lt;=1.5),D9,C9),C9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>IFERROR(IF(ISBLANK(D9),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D9),"Ignored: error value",IF(NOT(ISNUMBER(D9)),"Ignored: not a number",IF(OR(D9&lt;0.5,D9&gt;1.5),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>0.5 to 1.5</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>tail_factor.high</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Cohort development factor beyond observed history, high</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="48" t="n"/>
+      <c r="E10" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D10),D10&gt;=0.5,D10&lt;=1.5),D10,C10),C10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>IFERROR(IF(ISBLANK(D10),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D10),"Ignored: error value",IF(NOT(ISNUMBER(D10)),"Ignored: not a number",IF(OR(D10&lt;0.5,D10&gt;1.5),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>0.5 to 1.5</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>ent_usage_ratio.low</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Enterprise steady-state usage vs commitment, low</t>
+        </is>
+      </c>
+      <c r="C11" s="50" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D11" s="51" t="n"/>
+      <c r="E11" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D11),D11&gt;=0,D11&lt;=3),D11,C11),C11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>IFERROR(IF(ISBLANK(D11),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D11),"Ignored: error value",IF(NOT(ISNUMBER(D11)),"Ignored: not a number",IF(OR(D11&lt;0,D11&gt;3),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>0 to 3</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>ent_usage_ratio.base</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Enterprise steady-state usage vs commitment, base</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="51" t="n"/>
+      <c r="E12" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D12),D12&gt;=0,D12&lt;=3),D12,C12),C12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="3">
+        <f>IFERROR(IF(ISBLANK(D12),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D12),"Ignored: error value",IF(NOT(ISNUMBER(D12)),"Ignored: not a number",IF(OR(D12&lt;0,D12&gt;3),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>0 to 3</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ent_usage_ratio.high</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Enterprise steady-state usage vs commitment, high</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D13" s="51" t="n"/>
+      <c r="E13" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D13),D13&gt;=0,D13&lt;=3),D13,C13),C13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>IFERROR(IF(ISBLANK(D13),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D13),"Ignored: error value",IF(NOT(ISNUMBER(D13)),"Ignored: not a number",IF(OR(D13&lt;0,D13&gt;3),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>0 to 3</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>ent_growth.low</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Enterprise monthly growth after ramp, low</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D14),D14&gt;=-0.5,D14&lt;=1),D14,C14),C14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
+        <f>IFERROR(IF(ISBLANK(D14),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D14),"Ignored: error value",IF(NOT(ISNUMBER(D14)),"Ignored: not a number",IF(OR(D14&lt;-0.5,D14&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>-0.5 to 1</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>ent_growth.base</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Enterprise monthly growth after ramp, base</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D15" s="51" t="n"/>
+      <c r="E15" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D15),D15&gt;=-0.5,D15&lt;=1),D15,C15),C15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="3">
+        <f>IFERROR(IF(ISBLANK(D15),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D15),"Ignored: error value",IF(NOT(ISNUMBER(D15)),"Ignored: not a number",IF(OR(D15&lt;-0.5,D15&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>-0.5 to 1</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>ent_growth.high</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: Enterprise monthly growth after ramp, high</t>
+        </is>
+      </c>
+      <c r="C16" s="50" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D16" s="51" t="n"/>
+      <c r="E16" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D16),D16&gt;=-0.5,D16&lt;=1),D16,C16),C16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="3">
+        <f>IFERROR(IF(ISBLANK(D16),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D16),"Ignored: error value",IF(NOT(ISNUMBER(D16)),"Ignored: not a number",IF(OR(D16&lt;-0.5,D16&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>-0.5 to 1</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>signup_growth.low</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: new signups monthly growth, low</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="51" t="n"/>
+      <c r="E17" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D17),D17&gt;=-0.5,D17&lt;=1),D17,C17),C17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="3">
+        <f>IFERROR(IF(ISBLANK(D17),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D17),"Ignored: error value",IF(NOT(ISNUMBER(D17)),"Ignored: not a number",IF(OR(D17&lt;-0.5,D17&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>-0.5 to 1</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>gateway_growth_decay</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: gateway growth decay (base)</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="48" t="n"/>
+      <c r="E18" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D18),D18&gt;=0,D18&lt;=2),D18,C18),C18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="3">
+        <f>IFERROR(IF(ISBLANK(D18),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D18),"Ignored: error value",IF(NOT(ISNUMBER(D18)),"Ignored: not a number",IF(OR(D18&lt;0,D18&gt;2),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>0 to 2</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>ent_ramp_days</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: enterprise ramp length (days)</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="n">
+        <v>60</v>
+      </c>
+      <c r="D19" s="53" t="n"/>
+      <c r="E19" s="44">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D19),D19&gt;=1,D19&lt;=365),D19,C19),C19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="3">
+        <f>IFERROR(IF(ISBLANK(D19),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D19),"Ignored: error value",IF(NOT(ISNUMBER(D19)),"Ignored: not a number",IF(OR(D19&lt;1,D19&gt;365),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>1 to 365</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>price.self_serve</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: self-serve net $ per M tokens (price-change test)</t>
+        </is>
+      </c>
+      <c r="C20" s="26">
+        <f>IF(Monthly!M7=0,0,Monthly!M30/Monthly!M7)</f>
+        <v/>
+      </c>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="55">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D20),D20&gt;=0,D20&lt;=1),D20,C20),C20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="3">
+        <f>IFERROR(IF(ISBLANK(D20),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D20),"Ignored: error value",IF(NOT(ISNUMBER(D20)),"Ignored: not a number",IF(OR(D20&lt;0,D20&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>price.gateway</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: gateway net $ per M tokens (price-change test)</t>
+        </is>
+      </c>
+      <c r="C21" s="26">
+        <f>IF(Monthly!M8=0,0,Monthly!M31/Monthly!M8)</f>
+        <v/>
+      </c>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="55">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D21),D21&gt;=0,D21&lt;=1),D21,C21),C21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>IFERROR(IF(ISBLANK(D21),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D21),"Ignored: error value",IF(NOT(ISNUMBER(D21)),"Ignored: not a number",IF(OR(D21&lt;0,D21&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>price.list</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Forecast: list $ per M tokens for pipeline deals</t>
+        </is>
+      </c>
+      <c r="C22" s="26">
+        <f>Data_Params!$B$4</f>
+        <v/>
+      </c>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="55">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D22),D22&gt;=0,D22&lt;=1),D22,C22),C22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="3">
+        <f>IFERROR(IF(ISBLANK(D22),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D22),"Ignored: error value",IF(NOT(ISNUMBER(D22)),"Ignored: not a number",IF(OR(D22&lt;0,D22&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>capacity.gpu_tokens_per_sec</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Tokens per second per busy GPU</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="n">
+        <v>20604</v>
+      </c>
+      <c r="D23" s="53" t="n"/>
+      <c r="E23" s="44">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D23),D23&gt;=1,D23&lt;=10000000),D23,C23),C23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>IFERROR(IF(ISBLANK(D23),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D23),"Ignored: error value",IF(NOT(ISNUMBER(D23)),"Ignored: not a number",IF(OR(D23&lt;1,D23&gt;10000000),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>1 to 1e+07</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>capacity.peak_utilization</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Target utilization at peak</t>
+        </is>
+      </c>
+      <c r="C24" s="50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D24" s="51" t="n"/>
+      <c r="E24" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D24),D24&gt;=0.05,D24&lt;=1),D24,C24),C24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="3">
+        <f>IFERROR(IF(ISBLANK(D24),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D24),"Ignored: error value",IF(NOT(ISNUMBER(D24)),"Ignored: not a number",IF(OR(D24&lt;0.05,D24&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>0.05 to 1</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>capacity.reserved_rate</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Reserved rate ($ / GPU-hour)</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="58">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D25),D25&gt;=0,D25&lt;=100),D25,C25),C25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="3">
+        <f>IFERROR(IF(ISBLANK(D25),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D25),"Ignored: error value",IF(NOT(ISNUMBER(D25)),"Ignored: not a number",IF(OR(D25&lt;0,D25&gt;100),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>0 to 100</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>capacity.on_demand_rate</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: On-demand rate ($ / GPU-hour)</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="58">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D26),D26&gt;=0,D26&lt;=100),D26,C26),C26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="3">
+        <f>IFERROR(IF(ISBLANK(D26),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D26),"Ignored: error value",IF(NOT(ISNUMBER(D26)),"Ignored: not a number",IF(OR(D26&lt;0,D26&gt;100),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>0 to 100</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>capacity.peak_ratio_override</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Peak hour / average (override if no hourly data)</t>
+        </is>
+      </c>
+      <c r="C27" s="47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D27" s="48" t="n"/>
+      <c r="E27" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D27),D27&gt;=1,D27&lt;=20),D27,C27),C27)</f>
+        <v/>
+      </c>
+      <c r="F27" s="3">
+        <f>IFERROR(IF(ISBLANK(D27),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D27),"Ignored: error value",IF(NOT(ISNUMBER(D27)),"Ignored: not a number",IF(OR(D27&lt;1,D27&gt;20),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>1 to 20</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>capacity.base_ratio_override</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Quietest hour / average (override if no hourly data)</t>
+        </is>
+      </c>
+      <c r="C28" s="47" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D28" s="48" t="n"/>
+      <c r="E28" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D28),D28&gt;=0,D28&lt;=1),D28,C28),C28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>IFERROR(IF(ISBLANK(D28),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D28),"Ignored: error value",IF(NOT(ISNUMBER(D28)),"Ignored: not a number",IF(OR(D28&lt;0,D28&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>0 to 1</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Manual adjustments to net revenue (credit notes, corrections). Shown as their own line on Monthly, included in totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Month = any date in the month. Segment = pick from the list. Amount in $ (negative reduces revenue). Ignored unless all three are valid and the month is in the 12-month window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Amount ($)</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Approved by</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Month used</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Amount used ($)</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="59" t="n"/>
+      <c r="B46" s="60" t="n"/>
+      <c r="C46" s="57" t="n"/>
+      <c r="D46" s="61" t="n"/>
+      <c r="E46" s="61" t="n"/>
+      <c r="F46" s="28">
+        <f>IFERROR(IF(ISNUMBER(A46),DATE(YEAR(A46),MONTH(A46),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F46),ISNUMBER(C46),OR(B46="enterprise",B46="self_serve",B46="gateway_aggregate",B46="unmatched"),F46&gt;=Data_Params!$B$3,F46&lt;=Data_Params!$B$2),C46,0),0)</f>
+        <v/>
+      </c>
+      <c r="H46" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A46),ISBLANK(B46),ISBLANK(C46)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A46),ISERROR(B46),ISERROR(C46)),"Ignored: error value",IF(NOT(ISNUMBER(F46)),"Ignored: month is not a date",IF(NOT(OR(B46="enterprise",B46="self_serve",B46="gateway_aggregate",B46="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C46)),"Ignored: amount is not a number",IF(OR(F46&lt;Data_Params!$B$3,F46&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="n"/>
+      <c r="B47" s="60" t="n"/>
+      <c r="C47" s="57" t="n"/>
+      <c r="D47" s="61" t="n"/>
+      <c r="E47" s="61" t="n"/>
+      <c r="F47" s="28">
+        <f>IFERROR(IF(ISNUMBER(A47),DATE(YEAR(A47),MONTH(A47),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F47),ISNUMBER(C47),OR(B47="enterprise",B47="self_serve",B47="gateway_aggregate",B47="unmatched"),F47&gt;=Data_Params!$B$3,F47&lt;=Data_Params!$B$2),C47,0),0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A47),ISBLANK(B47),ISBLANK(C47)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A47),ISERROR(B47),ISERROR(C47)),"Ignored: error value",IF(NOT(ISNUMBER(F47)),"Ignored: month is not a date",IF(NOT(OR(B47="enterprise",B47="self_serve",B47="gateway_aggregate",B47="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C47)),"Ignored: amount is not a number",IF(OR(F47&lt;Data_Params!$B$3,F47&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="n"/>
+      <c r="B48" s="60" t="n"/>
+      <c r="C48" s="57" t="n"/>
+      <c r="D48" s="61" t="n"/>
+      <c r="E48" s="61" t="n"/>
+      <c r="F48" s="28">
+        <f>IFERROR(IF(ISNUMBER(A48),DATE(YEAR(A48),MONTH(A48),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F48),ISNUMBER(C48),OR(B48="enterprise",B48="self_serve",B48="gateway_aggregate",B48="unmatched"),F48&gt;=Data_Params!$B$3,F48&lt;=Data_Params!$B$2),C48,0),0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A48),ISBLANK(B48),ISBLANK(C48)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A48),ISERROR(B48),ISERROR(C48)),"Ignored: error value",IF(NOT(ISNUMBER(F48)),"Ignored: month is not a date",IF(NOT(OR(B48="enterprise",B48="self_serve",B48="gateway_aggregate",B48="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C48)),"Ignored: amount is not a number",IF(OR(F48&lt;Data_Params!$B$3,F48&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="59" t="n"/>
+      <c r="B49" s="60" t="n"/>
+      <c r="C49" s="57" t="n"/>
+      <c r="D49" s="61" t="n"/>
+      <c r="E49" s="61" t="n"/>
+      <c r="F49" s="28">
+        <f>IFERROR(IF(ISNUMBER(A49),DATE(YEAR(A49),MONTH(A49),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F49),ISNUMBER(C49),OR(B49="enterprise",B49="self_serve",B49="gateway_aggregate",B49="unmatched"),F49&gt;=Data_Params!$B$3,F49&lt;=Data_Params!$B$2),C49,0),0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A49),ISBLANK(B49),ISBLANK(C49)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A49),ISERROR(B49),ISERROR(C49)),"Ignored: error value",IF(NOT(ISNUMBER(F49)),"Ignored: month is not a date",IF(NOT(OR(B49="enterprise",B49="self_serve",B49="gateway_aggregate",B49="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C49)),"Ignored: amount is not a number",IF(OR(F49&lt;Data_Params!$B$3,F49&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="n"/>
+      <c r="B50" s="60" t="n"/>
+      <c r="C50" s="57" t="n"/>
+      <c r="D50" s="61" t="n"/>
+      <c r="E50" s="61" t="n"/>
+      <c r="F50" s="28">
+        <f>IFERROR(IF(ISNUMBER(A50),DATE(YEAR(A50),MONTH(A50),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F50),ISNUMBER(C50),OR(B50="enterprise",B50="self_serve",B50="gateway_aggregate",B50="unmatched"),F50&gt;=Data_Params!$B$3,F50&lt;=Data_Params!$B$2),C50,0),0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A50),ISBLANK(B50),ISBLANK(C50)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A50),ISERROR(B50),ISERROR(C50)),"Ignored: error value",IF(NOT(ISNUMBER(F50)),"Ignored: month is not a date",IF(NOT(OR(B50="enterprise",B50="self_serve",B50="gateway_aggregate",B50="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C50)),"Ignored: amount is not a number",IF(OR(F50&lt;Data_Params!$B$3,F50&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="n"/>
+      <c r="B51" s="60" t="n"/>
+      <c r="C51" s="57" t="n"/>
+      <c r="D51" s="61" t="n"/>
+      <c r="E51" s="61" t="n"/>
+      <c r="F51" s="28">
+        <f>IFERROR(IF(ISNUMBER(A51),DATE(YEAR(A51),MONTH(A51),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F51),ISNUMBER(C51),OR(B51="enterprise",B51="self_serve",B51="gateway_aggregate",B51="unmatched"),F51&gt;=Data_Params!$B$3,F51&lt;=Data_Params!$B$2),C51,0),0)</f>
+        <v/>
+      </c>
+      <c r="H51" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A51),ISBLANK(B51),ISBLANK(C51)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A51),ISERROR(B51),ISERROR(C51)),"Ignored: error value",IF(NOT(ISNUMBER(F51)),"Ignored: month is not a date",IF(NOT(OR(B51="enterprise",B51="self_serve",B51="gateway_aggregate",B51="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C51)),"Ignored: amount is not a number",IF(OR(F51&lt;Data_Params!$B$3,F51&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="59" t="n"/>
+      <c r="B52" s="60" t="n"/>
+      <c r="C52" s="57" t="n"/>
+      <c r="D52" s="61" t="n"/>
+      <c r="E52" s="61" t="n"/>
+      <c r="F52" s="28">
+        <f>IFERROR(IF(ISNUMBER(A52),DATE(YEAR(A52),MONTH(A52),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F52),ISNUMBER(C52),OR(B52="enterprise",B52="self_serve",B52="gateway_aggregate",B52="unmatched"),F52&gt;=Data_Params!$B$3,F52&lt;=Data_Params!$B$2),C52,0),0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A52),ISBLANK(B52),ISBLANK(C52)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A52),ISERROR(B52),ISERROR(C52)),"Ignored: error value",IF(NOT(ISNUMBER(F52)),"Ignored: month is not a date",IF(NOT(OR(B52="enterprise",B52="self_serve",B52="gateway_aggregate",B52="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C52)),"Ignored: amount is not a number",IF(OR(F52&lt;Data_Params!$B$3,F52&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="59" t="n"/>
+      <c r="B53" s="60" t="n"/>
+      <c r="C53" s="57" t="n"/>
+      <c r="D53" s="61" t="n"/>
+      <c r="E53" s="61" t="n"/>
+      <c r="F53" s="28">
+        <f>IFERROR(IF(ISNUMBER(A53),DATE(YEAR(A53),MONTH(A53),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F53),ISNUMBER(C53),OR(B53="enterprise",B53="self_serve",B53="gateway_aggregate",B53="unmatched"),F53&gt;=Data_Params!$B$3,F53&lt;=Data_Params!$B$2),C53,0),0)</f>
+        <v/>
+      </c>
+      <c r="H53" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A53),ISBLANK(B53),ISBLANK(C53)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A53),ISERROR(B53),ISERROR(C53)),"Ignored: error value",IF(NOT(ISNUMBER(F53)),"Ignored: month is not a date",IF(NOT(OR(B53="enterprise",B53="self_serve",B53="gateway_aggregate",B53="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C53)),"Ignored: amount is not a number",IF(OR(F53&lt;Data_Params!$B$3,F53&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="59" t="n"/>
+      <c r="B54" s="60" t="n"/>
+      <c r="C54" s="57" t="n"/>
+      <c r="D54" s="61" t="n"/>
+      <c r="E54" s="61" t="n"/>
+      <c r="F54" s="28">
+        <f>IFERROR(IF(ISNUMBER(A54),DATE(YEAR(A54),MONTH(A54),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F54),ISNUMBER(C54),OR(B54="enterprise",B54="self_serve",B54="gateway_aggregate",B54="unmatched"),F54&gt;=Data_Params!$B$3,F54&lt;=Data_Params!$B$2),C54,0),0)</f>
+        <v/>
+      </c>
+      <c r="H54" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A54),ISBLANK(B54),ISBLANK(C54)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A54),ISERROR(B54),ISERROR(C54)),"Ignored: error value",IF(NOT(ISNUMBER(F54)),"Ignored: month is not a date",IF(NOT(OR(B54="enterprise",B54="self_serve",B54="gateway_aggregate",B54="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C54)),"Ignored: amount is not a number",IF(OR(F54&lt;Data_Params!$B$3,F54&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="59" t="n"/>
+      <c r="B55" s="60" t="n"/>
+      <c r="C55" s="57" t="n"/>
+      <c r="D55" s="61" t="n"/>
+      <c r="E55" s="61" t="n"/>
+      <c r="F55" s="28">
+        <f>IFERROR(IF(ISNUMBER(A55),DATE(YEAR(A55),MONTH(A55),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F55),ISNUMBER(C55),OR(B55="enterprise",B55="self_serve",B55="gateway_aggregate",B55="unmatched"),F55&gt;=Data_Params!$B$3,F55&lt;=Data_Params!$B$2),C55,0),0)</f>
+        <v/>
+      </c>
+      <c r="H55" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A55),ISBLANK(B55),ISBLANK(C55)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A55),ISERROR(B55),ISERROR(C55)),"Ignored: error value",IF(NOT(ISNUMBER(F55)),"Ignored: month is not a date",IF(NOT(OR(B55="enterprise",B55="self_serve",B55="gateway_aggregate",B55="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C55)),"Ignored: amount is not a number",IF(OR(F55&lt;Data_Params!$B$3,F55&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="59" t="n"/>
+      <c r="B56" s="60" t="n"/>
+      <c r="C56" s="57" t="n"/>
+      <c r="D56" s="61" t="n"/>
+      <c r="E56" s="61" t="n"/>
+      <c r="F56" s="28">
+        <f>IFERROR(IF(ISNUMBER(A56),DATE(YEAR(A56),MONTH(A56),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F56),ISNUMBER(C56),OR(B56="enterprise",B56="self_serve",B56="gateway_aggregate",B56="unmatched"),F56&gt;=Data_Params!$B$3,F56&lt;=Data_Params!$B$2),C56,0),0)</f>
+        <v/>
+      </c>
+      <c r="H56" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A56),ISBLANK(B56),ISBLANK(C56)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A56),ISERROR(B56),ISERROR(C56)),"Ignored: error value",IF(NOT(ISNUMBER(F56)),"Ignored: month is not a date",IF(NOT(OR(B56="enterprise",B56="self_serve",B56="gateway_aggregate",B56="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C56)),"Ignored: amount is not a number",IF(OR(F56&lt;Data_Params!$B$3,F56&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="59" t="n"/>
+      <c r="B57" s="60" t="n"/>
+      <c r="C57" s="57" t="n"/>
+      <c r="D57" s="61" t="n"/>
+      <c r="E57" s="61" t="n"/>
+      <c r="F57" s="28">
+        <f>IFERROR(IF(ISNUMBER(A57),DATE(YEAR(A57),MONTH(A57),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F57),ISNUMBER(C57),OR(B57="enterprise",B57="self_serve",B57="gateway_aggregate",B57="unmatched"),F57&gt;=Data_Params!$B$3,F57&lt;=Data_Params!$B$2),C57,0),0)</f>
+        <v/>
+      </c>
+      <c r="H57" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A57),ISBLANK(B57),ISBLANK(C57)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A57),ISERROR(B57),ISERROR(C57)),"Ignored: error value",IF(NOT(ISNUMBER(F57)),"Ignored: month is not a date",IF(NOT(OR(B57="enterprise",B57="self_serve",B57="gateway_aggregate",B57="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C57)),"Ignored: amount is not a number",IF(OR(F57&lt;Data_Params!$B$3,F57&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="n"/>
+      <c r="B58" s="60" t="n"/>
+      <c r="C58" s="57" t="n"/>
+      <c r="D58" s="61" t="n"/>
+      <c r="E58" s="61" t="n"/>
+      <c r="F58" s="28">
+        <f>IFERROR(IF(ISNUMBER(A58),DATE(YEAR(A58),MONTH(A58),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F58),ISNUMBER(C58),OR(B58="enterprise",B58="self_serve",B58="gateway_aggregate",B58="unmatched"),F58&gt;=Data_Params!$B$3,F58&lt;=Data_Params!$B$2),C58,0),0)</f>
+        <v/>
+      </c>
+      <c r="H58" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A58),ISBLANK(B58),ISBLANK(C58)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A58),ISERROR(B58),ISERROR(C58)),"Ignored: error value",IF(NOT(ISNUMBER(F58)),"Ignored: month is not a date",IF(NOT(OR(B58="enterprise",B58="self_serve",B58="gateway_aggregate",B58="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C58)),"Ignored: amount is not a number",IF(OR(F58&lt;Data_Params!$B$3,F58&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="n"/>
+      <c r="B59" s="60" t="n"/>
+      <c r="C59" s="57" t="n"/>
+      <c r="D59" s="61" t="n"/>
+      <c r="E59" s="61" t="n"/>
+      <c r="F59" s="28">
+        <f>IFERROR(IF(ISNUMBER(A59),DATE(YEAR(A59),MONTH(A59),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F59),ISNUMBER(C59),OR(B59="enterprise",B59="self_serve",B59="gateway_aggregate",B59="unmatched"),F59&gt;=Data_Params!$B$3,F59&lt;=Data_Params!$B$2),C59,0),0)</f>
+        <v/>
+      </c>
+      <c r="H59" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A59),ISBLANK(B59),ISBLANK(C59)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A59),ISERROR(B59),ISERROR(C59)),"Ignored: error value",IF(NOT(ISNUMBER(F59)),"Ignored: month is not a date",IF(NOT(OR(B59="enterprise",B59="self_serve",B59="gateway_aggregate",B59="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C59)),"Ignored: amount is not a number",IF(OR(F59&lt;Data_Params!$B$3,F59&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="59" t="n"/>
+      <c r="B60" s="60" t="n"/>
+      <c r="C60" s="57" t="n"/>
+      <c r="D60" s="61" t="n"/>
+      <c r="E60" s="61" t="n"/>
+      <c r="F60" s="28">
+        <f>IFERROR(IF(ISNUMBER(A60),DATE(YEAR(A60),MONTH(A60),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F60),ISNUMBER(C60),OR(B60="enterprise",B60="self_serve",B60="gateway_aggregate",B60="unmatched"),F60&gt;=Data_Params!$B$3,F60&lt;=Data_Params!$B$2),C60,0),0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A60),ISBLANK(B60),ISBLANK(C60)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A60),ISERROR(B60),ISERROR(C60)),"Ignored: error value",IF(NOT(ISNUMBER(F60)),"Ignored: month is not a date",IF(NOT(OR(B60="enterprise",B60="self_serve",B60="gateway_aggregate",B60="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C60)),"Ignored: amount is not a number",IF(OR(F60&lt;Data_Params!$B$3,F60&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="59" t="n"/>
+      <c r="B61" s="60" t="n"/>
+      <c r="C61" s="57" t="n"/>
+      <c r="D61" s="61" t="n"/>
+      <c r="E61" s="61" t="n"/>
+      <c r="F61" s="28">
+        <f>IFERROR(IF(ISNUMBER(A61),DATE(YEAR(A61),MONTH(A61),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F61),ISNUMBER(C61),OR(B61="enterprise",B61="self_serve",B61="gateway_aggregate",B61="unmatched"),F61&gt;=Data_Params!$B$3,F61&lt;=Data_Params!$B$2),C61,0),0)</f>
+        <v/>
+      </c>
+      <c r="H61" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A61),ISBLANK(B61),ISBLANK(C61)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A61),ISERROR(B61),ISERROR(C61)),"Ignored: error value",IF(NOT(ISNUMBER(F61)),"Ignored: month is not a date",IF(NOT(OR(B61="enterprise",B61="self_serve",B61="gateway_aggregate",B61="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C61)),"Ignored: amount is not a number",IF(OR(F61&lt;Data_Params!$B$3,F61&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="59" t="n"/>
+      <c r="B62" s="60" t="n"/>
+      <c r="C62" s="57" t="n"/>
+      <c r="D62" s="61" t="n"/>
+      <c r="E62" s="61" t="n"/>
+      <c r="F62" s="28">
+        <f>IFERROR(IF(ISNUMBER(A62),DATE(YEAR(A62),MONTH(A62),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F62),ISNUMBER(C62),OR(B62="enterprise",B62="self_serve",B62="gateway_aggregate",B62="unmatched"),F62&gt;=Data_Params!$B$3,F62&lt;=Data_Params!$B$2),C62,0),0)</f>
+        <v/>
+      </c>
+      <c r="H62" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A62),ISBLANK(B62),ISBLANK(C62)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A62),ISERROR(B62),ISERROR(C62)),"Ignored: error value",IF(NOT(ISNUMBER(F62)),"Ignored: month is not a date",IF(NOT(OR(B62="enterprise",B62="self_serve",B62="gateway_aggregate",B62="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C62)),"Ignored: amount is not a number",IF(OR(F62&lt;Data_Params!$B$3,F62&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="59" t="n"/>
+      <c r="B63" s="60" t="n"/>
+      <c r="C63" s="57" t="n"/>
+      <c r="D63" s="61" t="n"/>
+      <c r="E63" s="61" t="n"/>
+      <c r="F63" s="28">
+        <f>IFERROR(IF(ISNUMBER(A63),DATE(YEAR(A63),MONTH(A63),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F63),ISNUMBER(C63),OR(B63="enterprise",B63="self_serve",B63="gateway_aggregate",B63="unmatched"),F63&gt;=Data_Params!$B$3,F63&lt;=Data_Params!$B$2),C63,0),0)</f>
+        <v/>
+      </c>
+      <c r="H63" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A63),ISBLANK(B63),ISBLANK(C63)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A63),ISERROR(B63),ISERROR(C63)),"Ignored: error value",IF(NOT(ISNUMBER(F63)),"Ignored: month is not a date",IF(NOT(OR(B63="enterprise",B63="self_serve",B63="gateway_aggregate",B63="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C63)),"Ignored: amount is not a number",IF(OR(F63&lt;Data_Params!$B$3,F63&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="59" t="n"/>
+      <c r="B64" s="60" t="n"/>
+      <c r="C64" s="57" t="n"/>
+      <c r="D64" s="61" t="n"/>
+      <c r="E64" s="61" t="n"/>
+      <c r="F64" s="28">
+        <f>IFERROR(IF(ISNUMBER(A64),DATE(YEAR(A64),MONTH(A64),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F64),ISNUMBER(C64),OR(B64="enterprise",B64="self_serve",B64="gateway_aggregate",B64="unmatched"),F64&gt;=Data_Params!$B$3,F64&lt;=Data_Params!$B$2),C64,0),0)</f>
+        <v/>
+      </c>
+      <c r="H64" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A64),ISBLANK(B64),ISBLANK(C64)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A64),ISERROR(B64),ISERROR(C64)),"Ignored: error value",IF(NOT(ISNUMBER(F64)),"Ignored: month is not a date",IF(NOT(OR(B64="enterprise",B64="self_serve",B64="gateway_aggregate",B64="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C64)),"Ignored: amount is not a number",IF(OR(F64&lt;Data_Params!$B$3,F64&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="59" t="n"/>
+      <c r="B65" s="60" t="n"/>
+      <c r="C65" s="57" t="n"/>
+      <c r="D65" s="61" t="n"/>
+      <c r="E65" s="61" t="n"/>
+      <c r="F65" s="28">
+        <f>IFERROR(IF(ISNUMBER(A65),DATE(YEAR(A65),MONTH(A65),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F65),ISNUMBER(C65),OR(B65="enterprise",B65="self_serve",B65="gateway_aggregate",B65="unmatched"),F65&gt;=Data_Params!$B$3,F65&lt;=Data_Params!$B$2),C65,0),0)</f>
+        <v/>
+      </c>
+      <c r="H65" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A65),ISBLANK(B65),ISBLANK(C65)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A65),ISERROR(B65),ISERROR(C65)),"Ignored: error value",IF(NOT(ISNUMBER(F65)),"Ignored: month is not a date",IF(NOT(OR(B65="enterprise",B65="self_serve",B65="gateway_aggregate",B65="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C65)),"Ignored: amount is not a number",IF(OR(F65&lt;Data_Params!$B$3,F65&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="59" t="n"/>
+      <c r="B66" s="60" t="n"/>
+      <c r="C66" s="57" t="n"/>
+      <c r="D66" s="61" t="n"/>
+      <c r="E66" s="61" t="n"/>
+      <c r="F66" s="28">
+        <f>IFERROR(IF(ISNUMBER(A66),DATE(YEAR(A66),MONTH(A66),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F66),ISNUMBER(C66),OR(B66="enterprise",B66="self_serve",B66="gateway_aggregate",B66="unmatched"),F66&gt;=Data_Params!$B$3,F66&lt;=Data_Params!$B$2),C66,0),0)</f>
+        <v/>
+      </c>
+      <c r="H66" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A66),ISBLANK(B66),ISBLANK(C66)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A66),ISERROR(B66),ISERROR(C66)),"Ignored: error value",IF(NOT(ISNUMBER(F66)),"Ignored: month is not a date",IF(NOT(OR(B66="enterprise",B66="self_serve",B66="gateway_aggregate",B66="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C66)),"Ignored: amount is not a number",IF(OR(F66&lt;Data_Params!$B$3,F66&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="59" t="n"/>
+      <c r="B67" s="60" t="n"/>
+      <c r="C67" s="57" t="n"/>
+      <c r="D67" s="61" t="n"/>
+      <c r="E67" s="61" t="n"/>
+      <c r="F67" s="28">
+        <f>IFERROR(IF(ISNUMBER(A67),DATE(YEAR(A67),MONTH(A67),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G67" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F67),ISNUMBER(C67),OR(B67="enterprise",B67="self_serve",B67="gateway_aggregate",B67="unmatched"),F67&gt;=Data_Params!$B$3,F67&lt;=Data_Params!$B$2),C67,0),0)</f>
+        <v/>
+      </c>
+      <c r="H67" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A67),ISBLANK(B67),ISBLANK(C67)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A67),ISERROR(B67),ISERROR(C67)),"Ignored: error value",IF(NOT(ISNUMBER(F67)),"Ignored: month is not a date",IF(NOT(OR(B67="enterprise",B67="self_serve",B67="gateway_aggregate",B67="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C67)),"Ignored: amount is not a number",IF(OR(F67&lt;Data_Params!$B$3,F67&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="59" t="n"/>
+      <c r="B68" s="60" t="n"/>
+      <c r="C68" s="57" t="n"/>
+      <c r="D68" s="61" t="n"/>
+      <c r="E68" s="61" t="n"/>
+      <c r="F68" s="28">
+        <f>IFERROR(IF(ISNUMBER(A68),DATE(YEAR(A68),MONTH(A68),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F68),ISNUMBER(C68),OR(B68="enterprise",B68="self_serve",B68="gateway_aggregate",B68="unmatched"),F68&gt;=Data_Params!$B$3,F68&lt;=Data_Params!$B$2),C68,0),0)</f>
+        <v/>
+      </c>
+      <c r="H68" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A68),ISBLANK(B68),ISBLANK(C68)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A68),ISERROR(B68),ISERROR(C68)),"Ignored: error value",IF(NOT(ISNUMBER(F68)),"Ignored: month is not a date",IF(NOT(OR(B68="enterprise",B68="self_serve",B68="gateway_aggregate",B68="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C68)),"Ignored: amount is not a number",IF(OR(F68&lt;Data_Params!$B$3,F68&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="59" t="n"/>
+      <c r="B69" s="60" t="n"/>
+      <c r="C69" s="57" t="n"/>
+      <c r="D69" s="61" t="n"/>
+      <c r="E69" s="61" t="n"/>
+      <c r="F69" s="28">
+        <f>IFERROR(IF(ISNUMBER(A69),DATE(YEAR(A69),MONTH(A69),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F69),ISNUMBER(C69),OR(B69="enterprise",B69="self_serve",B69="gateway_aggregate",B69="unmatched"),F69&gt;=Data_Params!$B$3,F69&lt;=Data_Params!$B$2),C69,0),0)</f>
+        <v/>
+      </c>
+      <c r="H69" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A69),ISBLANK(B69),ISBLANK(C69)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A69),ISERROR(B69),ISERROR(C69)),"Ignored: error value",IF(NOT(ISNUMBER(F69)),"Ignored: month is not a date",IF(NOT(OR(B69="enterprise",B69="self_serve",B69="gateway_aggregate",B69="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C69)),"Ignored: amount is not a number",IF(OR(F69&lt;Data_Params!$B$3,F69&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="59" t="n"/>
+      <c r="B70" s="60" t="n"/>
+      <c r="C70" s="57" t="n"/>
+      <c r="D70" s="61" t="n"/>
+      <c r="E70" s="61" t="n"/>
+      <c r="F70" s="28">
+        <f>IFERROR(IF(ISNUMBER(A70),DATE(YEAR(A70),MONTH(A70),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F70),ISNUMBER(C70),OR(B70="enterprise",B70="self_serve",B70="gateway_aggregate",B70="unmatched"),F70&gt;=Data_Params!$B$3,F70&lt;=Data_Params!$B$2),C70,0),0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A70),ISBLANK(B70),ISBLANK(C70)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A70),ISERROR(B70),ISERROR(C70)),"Ignored: error value",IF(NOT(ISNUMBER(F70)),"Ignored: month is not a date",IF(NOT(OR(B70="enterprise",B70="self_serve",B70="gateway_aggregate",B70="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C70)),"Ignored: amount is not a number",IF(OR(F70&lt;Data_Params!$B$3,F70&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="59" t="n"/>
+      <c r="B71" s="60" t="n"/>
+      <c r="C71" s="57" t="n"/>
+      <c r="D71" s="61" t="n"/>
+      <c r="E71" s="61" t="n"/>
+      <c r="F71" s="28">
+        <f>IFERROR(IF(ISNUMBER(A71),DATE(YEAR(A71),MONTH(A71),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F71),ISNUMBER(C71),OR(B71="enterprise",B71="self_serve",B71="gateway_aggregate",B71="unmatched"),F71&gt;=Data_Params!$B$3,F71&lt;=Data_Params!$B$2),C71,0),0)</f>
+        <v/>
+      </c>
+      <c r="H71" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A71),ISBLANK(B71),ISBLANK(C71)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A71),ISERROR(B71),ISERROR(C71)),"Ignored: error value",IF(NOT(ISNUMBER(F71)),"Ignored: month is not a date",IF(NOT(OR(B71="enterprise",B71="self_serve",B71="gateway_aggregate",B71="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C71)),"Ignored: amount is not a number",IF(OR(F71&lt;Data_Params!$B$3,F71&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="59" t="n"/>
+      <c r="B72" s="60" t="n"/>
+      <c r="C72" s="57" t="n"/>
+      <c r="D72" s="61" t="n"/>
+      <c r="E72" s="61" t="n"/>
+      <c r="F72" s="28">
+        <f>IFERROR(IF(ISNUMBER(A72),DATE(YEAR(A72),MONTH(A72),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G72" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F72),ISNUMBER(C72),OR(B72="enterprise",B72="self_serve",B72="gateway_aggregate",B72="unmatched"),F72&gt;=Data_Params!$B$3,F72&lt;=Data_Params!$B$2),C72,0),0)</f>
+        <v/>
+      </c>
+      <c r="H72" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A72),ISBLANK(B72),ISBLANK(C72)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A72),ISERROR(B72),ISERROR(C72)),"Ignored: error value",IF(NOT(ISNUMBER(F72)),"Ignored: month is not a date",IF(NOT(OR(B72="enterprise",B72="self_serve",B72="gateway_aggregate",B72="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C72)),"Ignored: amount is not a number",IF(OR(F72&lt;Data_Params!$B$3,F72&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="59" t="n"/>
+      <c r="B73" s="60" t="n"/>
+      <c r="C73" s="57" t="n"/>
+      <c r="D73" s="61" t="n"/>
+      <c r="E73" s="61" t="n"/>
+      <c r="F73" s="28">
+        <f>IFERROR(IF(ISNUMBER(A73),DATE(YEAR(A73),MONTH(A73),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G73" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F73),ISNUMBER(C73),OR(B73="enterprise",B73="self_serve",B73="gateway_aggregate",B73="unmatched"),F73&gt;=Data_Params!$B$3,F73&lt;=Data_Params!$B$2),C73,0),0)</f>
+        <v/>
+      </c>
+      <c r="H73" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A73),ISBLANK(B73),ISBLANK(C73)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A73),ISERROR(B73),ISERROR(C73)),"Ignored: error value",IF(NOT(ISNUMBER(F73)),"Ignored: month is not a date",IF(NOT(OR(B73="enterprise",B73="self_serve",B73="gateway_aggregate",B73="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C73)),"Ignored: amount is not a number",IF(OR(F73&lt;Data_Params!$B$3,F73&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="59" t="n"/>
+      <c r="B74" s="60" t="n"/>
+      <c r="C74" s="57" t="n"/>
+      <c r="D74" s="61" t="n"/>
+      <c r="E74" s="61" t="n"/>
+      <c r="F74" s="28">
+        <f>IFERROR(IF(ISNUMBER(A74),DATE(YEAR(A74),MONTH(A74),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G74" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F74),ISNUMBER(C74),OR(B74="enterprise",B74="self_serve",B74="gateway_aggregate",B74="unmatched"),F74&gt;=Data_Params!$B$3,F74&lt;=Data_Params!$B$2),C74,0),0)</f>
+        <v/>
+      </c>
+      <c r="H74" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A74),ISBLANK(B74),ISBLANK(C74)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A74),ISERROR(B74),ISERROR(C74)),"Ignored: error value",IF(NOT(ISNUMBER(F74)),"Ignored: month is not a date",IF(NOT(OR(B74="enterprise",B74="self_serve",B74="gateway_aggregate",B74="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C74)),"Ignored: amount is not a number",IF(OR(F74&lt;Data_Params!$B$3,F74&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="59" t="n"/>
+      <c r="B75" s="60" t="n"/>
+      <c r="C75" s="57" t="n"/>
+      <c r="D75" s="61" t="n"/>
+      <c r="E75" s="61" t="n"/>
+      <c r="F75" s="28">
+        <f>IFERROR(IF(ISNUMBER(A75),DATE(YEAR(A75),MONTH(A75),1),""),"")</f>
+        <v/>
+      </c>
+      <c r="G75" s="17">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(F75),ISNUMBER(C75),OR(B75="enterprise",B75="self_serve",B75="gateway_aggregate",B75="unmatched"),F75&gt;=Data_Params!$B$3,F75&lt;=Data_Params!$B$2),C75,0),0)</f>
+        <v/>
+      </c>
+      <c r="H75" s="3">
+        <f>IFERROR(IF(AND(ISBLANK(A75),ISBLANK(B75),ISBLANK(C75)),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(OR(ISERROR(A75),ISERROR(B75),ISERROR(C75)),"Ignored: error value",IF(NOT(ISNUMBER(F75)),"Ignored: month is not a date",IF(NOT(OR(B75="enterprise",B75="self_serve",B75="gateway_aggregate",B75="unmatched")),"Ignored: unknown segment",IF(NOT(ISNUMBER(C75)),"Ignored: amount is not a number",IF(OR(F75&lt;Data_Params!$B$3,F75&gt;Data_Params!$B$2),"Ignored: month outside the window","Applied"))))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F8:F39 H46:H75">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT(F8,7)="Ignored"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>F8="Applied"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4">
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>$C$4="ON"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="25">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ON or OFF" error="Choose ON or OFF." type="list">
+      <formula1>"ON,OFF"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Segment" error="Pick a segment from the list." type="list">
+      <formula1>"enterprise,self_serve,gateway_aggregate,unmatched"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="Enter an amount in dollars." type="decimal" operator="between">
+      <formula1>-100000000</formula1>
+      <formula2>100000000</formula2>
+    </dataValidation>
+    <dataValidation sqref="A46 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A57 A58 A59 A60 A61 A62 A63 A64 A65 A66 A67 A68 A69 A70 A71 A72 A73 A74 A75" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Month" error="Enter a date, e.g. 2027-02-01." type="date" operator="between">
+      <formula1>36526</formula1>
+      <formula2>73051</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0.5 to 1.5, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.5</formula1>
+      <formula2>1.5</formula2>
+    </dataValidation>
+    <dataValidation sqref="D9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0.5 to 1.5, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.5</formula1>
+      <formula2>1.5</formula2>
+    </dataValidation>
+    <dataValidation sqref="D10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0.5 to 1.5, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.5</formula1>
+      <formula2>1.5</formula2>
+    </dataValidation>
+    <dataValidation sqref="D11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 3, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation sqref="D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 3, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation sqref="D13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 3, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation sqref="D14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from -0.5 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>-0.5</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from -0.5 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>-0.5</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from -0.5 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>-0.5</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from -0.5 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>-0.5</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 2, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>2</formula2>
+    </dataValidation>
+    <dataValidation sqref="D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 365, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>1</formula1>
+      <formula2>365</formula2>
+    </dataValidation>
+    <dataValidation sqref="D20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 1e+07, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>1</formula1>
+      <formula2>10000000</formula2>
+    </dataValidation>
+    <dataValidation sqref="D24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0.05 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.05</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="D25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 100, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="D26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 100, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 20, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>1</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
+    <dataValidation sqref="D28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -9680,17 +11203,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -9702,7 +11225,7 @@
           <t>as_of_month</t>
         </is>
       </c>
-      <c r="B2" s="50" t="n"/>
+      <c r="B2" s="63" t="n"/>
       <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Last complete month in this close (first day of month)</t>
@@ -9715,7 +11238,7 @@
           <t>window_start</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
+      <c r="B3" s="63" t="n"/>
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>First month of the 12-month reporting window</t>
@@ -9800,7 +11323,7 @@
           <t>data_first_date</t>
         </is>
       </c>
-      <c r="B10" s="50" t="n"/>
+      <c r="B10" s="63" t="n"/>
       <c r="C10" s="7" t="inlineStr">
         <is>
           <t>First date with usage</t>
@@ -9813,7 +11336,7 @@
           <t>data_last_date</t>
         </is>
       </c>
-      <c r="B11" s="50" t="n"/>
+      <c r="B11" s="63" t="n"/>
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Last date with usage (on or before as-of month end)</t>
@@ -9873,7 +11396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -9889,17 +11412,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>calendar_days</t>
         </is>
@@ -9910,7 +11433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -9936,67 +11459,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>active_accounts</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>paying_accounts</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>billable_tokens</t>
         </is>
       </c>
-      <c r="G1" s="49" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>free_credit_tokens</t>
         </is>
       </c>
-      <c r="H1" s="49" t="inlineStr">
+      <c r="H1" s="62" t="inlineStr">
         <is>
           <t>free_credit_usd</t>
         </is>
       </c>
-      <c r="I1" s="49" t="inlineStr">
+      <c r="I1" s="62" t="inlineStr">
         <is>
           <t>list_value</t>
         </is>
       </c>
-      <c r="J1" s="49" t="inlineStr">
+      <c r="J1" s="62" t="inlineStr">
         <is>
           <t>usage_revenue</t>
         </is>
       </c>
-      <c r="K1" s="49" t="inlineStr">
+      <c r="K1" s="62" t="inlineStr">
         <is>
           <t>true_up</t>
         </is>
       </c>
-      <c r="L1" s="49" t="inlineStr">
+      <c r="L1" s="62" t="inlineStr">
         <is>
           <t>net_revenue</t>
         </is>
       </c>
-      <c r="M1" s="49" t="inlineStr">
+      <c r="M1" s="62" t="inlineStr">
         <is>
           <t>gateway_fees</t>
         </is>
@@ -10007,7 +11530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10023,17 +11546,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>use_case</t>
         </is>
@@ -10044,7 +11567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10061,22 +11584,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>use_case</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>billable_tokens</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>tokens_from_label</t>
         </is>
@@ -10087,7 +11610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10103,17 +11626,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>use_case</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>labelled_tokens</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>inferred_correctly</t>
         </is>
@@ -10124,7 +11647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10141,55 +11664,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>cohort</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>billable_tokens</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>active_accounts</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="008A939B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="49" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="49" t="inlineStr">
-        <is>
-          <t>billable_tokens</t>
         </is>
       </c>
     </row>
@@ -10248,6 +11740,15 @@
         <f>Data_Params!$B$12</f>
         <v/>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Overrides</t>
+        </is>
+      </c>
+      <c r="G3" s="5">
+        <f>Overrides!$C$5</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -10349,27 +11850,27 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>Monthly!H33</f>
+        <f>Monthly!H34</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>Monthly!I33</f>
+        <f>Monthly!I34</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>Monthly!J33</f>
+        <f>Monthly!J34</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>Monthly!K33</f>
+        <f>Monthly!K34</f>
         <v/>
       </c>
       <c r="F8" s="10">
-        <f>Monthly!L33</f>
+        <f>Monthly!L34</f>
         <v/>
       </c>
       <c r="G8" s="10">
-        <f>Monthly!M33</f>
+        <f>Monthly!M34</f>
         <v/>
       </c>
     </row>
@@ -10380,27 +11881,27 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>Monthly!H35</f>
+        <f>Monthly!H36</f>
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>Monthly!I35</f>
+        <f>Monthly!I36</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>Monthly!J35</f>
+        <f>Monthly!J36</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>Monthly!K35</f>
+        <f>Monthly!K36</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>Monthly!L35</f>
+        <f>Monthly!L36</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>Monthly!M35</f>
+        <f>Monthly!M36</f>
         <v/>
       </c>
     </row>
@@ -10411,27 +11912,27 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>Monthly!H36</f>
+        <f>Monthly!H37</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>Monthly!I36</f>
+        <f>Monthly!I37</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>Monthly!J36</f>
+        <f>Monthly!J37</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>Monthly!K36</f>
+        <f>Monthly!K37</f>
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>Monthly!L36</f>
+        <f>Monthly!L37</f>
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>Monthly!M36</f>
+        <f>Monthly!M37</f>
         <v/>
       </c>
     </row>
@@ -10442,27 +11943,27 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <f>Monthly!H37</f>
+        <f>Monthly!H38</f>
         <v/>
       </c>
       <c r="C11" s="13">
-        <f>Monthly!I37</f>
+        <f>Monthly!I38</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>Monthly!J37</f>
+        <f>Monthly!J38</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>Monthly!K37</f>
+        <f>Monthly!K38</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>Monthly!L37</f>
+        <f>Monthly!L38</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>Monthly!M37</f>
+        <f>Monthly!M38</f>
         <v/>
       </c>
     </row>
@@ -10473,27 +11974,27 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>Monthly!H43</f>
+        <f>Monthly!H44</f>
         <v/>
       </c>
       <c r="C12" s="12">
-        <f>Monthly!I43</f>
+        <f>Monthly!I44</f>
         <v/>
       </c>
       <c r="D12" s="12">
-        <f>Monthly!J43</f>
+        <f>Monthly!J44</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>Monthly!K43</f>
+        <f>Monthly!K44</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>Monthly!L43</f>
+        <f>Monthly!L44</f>
         <v/>
       </c>
       <c r="G12" s="12">
-        <f>Monthly!M43</f>
+        <f>Monthly!M44</f>
         <v/>
       </c>
     </row>
@@ -10504,27 +12005,27 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>Monthly!H44</f>
+        <f>Monthly!H45</f>
         <v/>
       </c>
       <c r="C13" s="12">
-        <f>Monthly!I44</f>
+        <f>Monthly!I45</f>
         <v/>
       </c>
       <c r="D13" s="12">
-        <f>Monthly!J44</f>
+        <f>Monthly!J45</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>Monthly!K44</f>
+        <f>Monthly!K45</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>Monthly!L44</f>
+        <f>Monthly!L45</f>
         <v/>
       </c>
       <c r="G13" s="12">
-        <f>Monthly!M44</f>
+        <f>Monthly!M45</f>
         <v/>
       </c>
     </row>
@@ -10535,27 +12036,27 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>Monthly!H45</f>
+        <f>Monthly!H46</f>
         <v/>
       </c>
       <c r="C14" s="11">
-        <f>Monthly!I45</f>
+        <f>Monthly!I46</f>
         <v/>
       </c>
       <c r="D14" s="11">
-        <f>Monthly!J45</f>
+        <f>Monthly!J46</f>
         <v/>
       </c>
       <c r="E14" s="11">
-        <f>Monthly!K45</f>
+        <f>Monthly!K46</f>
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>Monthly!L45</f>
+        <f>Monthly!L46</f>
         <v/>
       </c>
       <c r="G14" s="11">
-        <f>Monthly!M45</f>
+        <f>Monthly!M46</f>
         <v/>
       </c>
     </row>
@@ -10779,11 +12280,47 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="A37:G37"/>
   </mergeCells>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(Overrides!$C$4="ON",COUNTIF(Overrides!$F$8:$F$39,"Applied")+COUNTIF(Overrides!$H$46:$H$75,"Applied")&gt;0)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008A939B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="62" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="inlineStr">
+        <is>
+          <t>billable_tokens</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10800,22 +12337,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>cohort</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>signups</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>added_payment_method</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>payment_flag_known</t>
         </is>
@@ -10826,7 +12363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10847,42 +12384,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>account_id</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>start_date</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>end_date</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>monthly_commit_usd</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>unit_price_per_mtok</t>
         </is>
       </c>
-      <c r="G1" s="49" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>discount_pct</t>
         </is>
       </c>
-      <c r="H1" s="49" t="inlineStr">
+      <c r="H1" s="62" t="inlineStr">
         <is>
           <t>last7_btok_per_day</t>
         </is>
@@ -10893,7 +12430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10912,32 +12449,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>billable_tokens</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>usage_revenue</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>commitment</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>true_up</t>
         </is>
@@ -10948,7 +12485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -10969,42 +12506,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>deal_id</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>customer</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>probability</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>expected_monthly_commit_usd</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>expected_start</t>
         </is>
       </c>
-      <c r="G1" s="49" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>expected_discount_pct</t>
         </is>
       </c>
-      <c r="H1" s="49" t="inlineStr">
+      <c r="H1" s="62" t="inlineStr">
         <is>
           <t>use_cases</t>
         </is>
@@ -11015,7 +12552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -11036,42 +12573,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>account_id</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>channel</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>billable_tokens</t>
         </is>
       </c>
-      <c r="G1" s="49" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>net_revenue</t>
         </is>
       </c>
-      <c r="H1" s="49" t="inlineStr">
+      <c r="H1" s="62" t="inlineStr">
         <is>
           <t>share_of_revenue</t>
         </is>
@@ -11082,7 +12619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -11103,42 +12640,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>check_no</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>check_name</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>expected</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="F1" s="49" t="inlineStr">
+      <c r="F1" s="62" t="inlineStr">
         <is>
           <t>usd_impact</t>
         </is>
       </c>
-      <c r="G1" s="49" t="inlineStr">
+      <c r="G1" s="62" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="49" t="inlineStr">
+      <c r="H1" s="62" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
@@ -11149,7 +12686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -11165,17 +12702,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>calls_ok</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>calls_failed</t>
         </is>
@@ -11186,7 +12723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -11201,12 +12738,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>hour_start</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>tokens</t>
         </is>
@@ -11217,7 +12754,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008A939B"/>
@@ -11235,27 +12772,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>close_month</t>
         </is>
       </c>
-      <c r="B1" s="49" t="inlineStr">
+      <c r="B1" s="62" t="inlineStr">
         <is>
           <t>target_month</t>
         </is>
       </c>
-      <c r="C1" s="49" t="inlineStr">
+      <c r="C1" s="62" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="D1" s="49" t="inlineStr">
+      <c r="D1" s="62" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="E1" s="49" t="inlineStr">
+      <c r="E1" s="62" t="inlineStr">
         <is>
           <t>btok_per_day</t>
         </is>
@@ -17089,7 +18626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -18486,625 +20023,680 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Manual adjustments (Overrides tab)</t>
+        </is>
+      </c>
+      <c r="B33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,B$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="C33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,C$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="D33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,D$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="E33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,E$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,F$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="G33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,G$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="H33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,H$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="I33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,I$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="J33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,J$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="K33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,K$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="L33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,L$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="M33" s="10">
+        <f>SUMIFS(Overrides!$G$46:$G$75,Overrides!$F$46:$F$75,M$4)/1E3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Total net revenue</t>
         </is>
       </c>
-      <c r="B33" s="22">
-        <f>SUM(B29:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="22">
-        <f>SUM(C29:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="22">
-        <f>SUM(D29:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="22">
-        <f>SUM(E29:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="22">
-        <f>SUM(F29:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="22">
-        <f>SUM(G29:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="22">
-        <f>SUM(H29:H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="22">
-        <f>SUM(I29:I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="22">
-        <f>SUM(J29:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="22">
-        <f>SUM(K29:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="22">
-        <f>SUM(L29:L32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="22">
-        <f>SUM(M29:M32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  of which enterprise true-ups</t>
-        </is>
-      </c>
-      <c r="B34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,B$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="C34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,C$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="D34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,D$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="E34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,E$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="F34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,F$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="G34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,G$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="H34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,H$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="I34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,I$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="J34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,J$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="K34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,K$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="L34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,L$4)/1E3</f>
-        <v/>
-      </c>
-      <c r="M34" s="21">
-        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,M$4)/1E3</f>
+      <c r="B34" s="22">
+        <f>SUM(B29:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="22">
+        <f>SUM(C29:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="22">
+        <f>SUM(D29:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="22">
+        <f>SUM(E29:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="22">
+        <f>SUM(F29:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="22">
+        <f>SUM(G29:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="22">
+        <f>SUM(H29:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="22">
+        <f>SUM(I29:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="22">
+        <f>SUM(J29:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="22">
+        <f>SUM(K29:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="22">
+        <f>SUM(L29:L33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="22">
+        <f>SUM(M29:M33)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Annualized run-rate ($k)</t>
-        </is>
-      </c>
-      <c r="B35" s="23">
-        <f>IF(B11=0,0,B33/B11*365)</f>
-        <v/>
-      </c>
-      <c r="C35" s="23">
-        <f>IF(C11=0,0,C33/C11*365)</f>
-        <v/>
-      </c>
-      <c r="D35" s="23">
-        <f>IF(D11=0,0,D33/D11*365)</f>
-        <v/>
-      </c>
-      <c r="E35" s="23">
-        <f>IF(E11=0,0,E33/E11*365)</f>
-        <v/>
-      </c>
-      <c r="F35" s="23">
-        <f>IF(F11=0,0,F33/F11*365)</f>
-        <v/>
-      </c>
-      <c r="G35" s="23">
-        <f>IF(G11=0,0,G33/G11*365)</f>
-        <v/>
-      </c>
-      <c r="H35" s="23">
-        <f>IF(H11=0,0,H33/H11*365)</f>
-        <v/>
-      </c>
-      <c r="I35" s="23">
-        <f>IF(I11=0,0,I33/I11*365)</f>
-        <v/>
-      </c>
-      <c r="J35" s="23">
-        <f>IF(J11=0,0,J33/J11*365)</f>
-        <v/>
-      </c>
-      <c r="K35" s="23">
-        <f>IF(K11=0,0,K33/K11*365)</f>
-        <v/>
-      </c>
-      <c r="L35" s="23">
-        <f>IF(L11=0,0,L33/L11*365)</f>
-        <v/>
-      </c>
-      <c r="M35" s="23">
-        <f>IF(M11=0,0,M33/M11*365)</f>
+          <t xml:space="preserve">  of which enterprise true-ups</t>
+        </is>
+      </c>
+      <c r="B35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,B$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="C35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,C$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="D35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,D$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="E35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,E$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="F35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,F$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="G35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,G$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="H35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,H$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="I35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,I$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="J35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,J$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="K35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,K$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="L35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,L$4)/1E3</f>
+        <v/>
+      </c>
+      <c r="M35" s="21">
+        <f>SUMIFS(Data_Monthly!$K:$K,Data_Monthly!$A:$A,M$4)/1E3</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Enterprise share of net revenue</t>
-        </is>
-      </c>
-      <c r="B36" s="25">
-        <f>IF(B33=0,0,B29/B33)</f>
-        <v/>
-      </c>
-      <c r="C36" s="25">
-        <f>IF(C33=0,0,C29/C33)</f>
-        <v/>
-      </c>
-      <c r="D36" s="25">
-        <f>IF(D33=0,0,D29/D33)</f>
-        <v/>
-      </c>
-      <c r="E36" s="25">
-        <f>IF(E33=0,0,E29/E33)</f>
-        <v/>
-      </c>
-      <c r="F36" s="25">
-        <f>IF(F33=0,0,F29/F33)</f>
-        <v/>
-      </c>
-      <c r="G36" s="25">
-        <f>IF(G33=0,0,G29/G33)</f>
-        <v/>
-      </c>
-      <c r="H36" s="25">
-        <f>IF(H33=0,0,H29/H33)</f>
-        <v/>
-      </c>
-      <c r="I36" s="25">
-        <f>IF(I33=0,0,I29/I33)</f>
-        <v/>
-      </c>
-      <c r="J36" s="25">
-        <f>IF(J33=0,0,J29/J33)</f>
-        <v/>
-      </c>
-      <c r="K36" s="25">
-        <f>IF(K33=0,0,K29/K33)</f>
-        <v/>
-      </c>
-      <c r="L36" s="25">
-        <f>IF(L33=0,0,L29/L33)</f>
-        <v/>
-      </c>
-      <c r="M36" s="25">
-        <f>IF(M33=0,0,M29/M33)</f>
+          <t>Annualized run-rate ($k)</t>
+        </is>
+      </c>
+      <c r="B36" s="23">
+        <f>IF(B11=0,0,B34/B11*365)</f>
+        <v/>
+      </c>
+      <c r="C36" s="23">
+        <f>IF(C11=0,0,C34/C11*365)</f>
+        <v/>
+      </c>
+      <c r="D36" s="23">
+        <f>IF(D11=0,0,D34/D11*365)</f>
+        <v/>
+      </c>
+      <c r="E36" s="23">
+        <f>IF(E11=0,0,E34/E11*365)</f>
+        <v/>
+      </c>
+      <c r="F36" s="23">
+        <f>IF(F11=0,0,F34/F11*365)</f>
+        <v/>
+      </c>
+      <c r="G36" s="23">
+        <f>IF(G11=0,0,G34/G11*365)</f>
+        <v/>
+      </c>
+      <c r="H36" s="23">
+        <f>IF(H11=0,0,H34/H11*365)</f>
+        <v/>
+      </c>
+      <c r="I36" s="23">
+        <f>IF(I11=0,0,I34/I11*365)</f>
+        <v/>
+      </c>
+      <c r="J36" s="23">
+        <f>IF(J11=0,0,J34/J11*365)</f>
+        <v/>
+      </c>
+      <c r="K36" s="23">
+        <f>IF(K11=0,0,K34/K11*365)</f>
+        <v/>
+      </c>
+      <c r="L36" s="23">
+        <f>IF(L11=0,0,L34/L11*365)</f>
+        <v/>
+      </c>
+      <c r="M36" s="23">
+        <f>IF(M11=0,0,M34/M11*365)</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>Enterprise share of net revenue</t>
+        </is>
+      </c>
+      <c r="B37" s="25">
+        <f>IF(B34=0,0,B29/B34)</f>
+        <v/>
+      </c>
+      <c r="C37" s="25">
+        <f>IF(C34=0,0,C29/C34)</f>
+        <v/>
+      </c>
+      <c r="D37" s="25">
+        <f>IF(D34=0,0,D29/D34)</f>
+        <v/>
+      </c>
+      <c r="E37" s="25">
+        <f>IF(E34=0,0,E29/E34)</f>
+        <v/>
+      </c>
+      <c r="F37" s="25">
+        <f>IF(F34=0,0,F29/F34)</f>
+        <v/>
+      </c>
+      <c r="G37" s="25">
+        <f>IF(G34=0,0,G29/G34)</f>
+        <v/>
+      </c>
+      <c r="H37" s="25">
+        <f>IF(H34=0,0,H29/H34)</f>
+        <v/>
+      </c>
+      <c r="I37" s="25">
+        <f>IF(I34=0,0,I29/I34)</f>
+        <v/>
+      </c>
+      <c r="J37" s="25">
+        <f>IF(J34=0,0,J29/J34)</f>
+        <v/>
+      </c>
+      <c r="K37" s="25">
+        <f>IF(K34=0,0,K29/K34)</f>
+        <v/>
+      </c>
+      <c r="L37" s="25">
+        <f>IF(L34=0,0,L29/L34)</f>
+        <v/>
+      </c>
+      <c r="M37" s="25">
+        <f>IF(M34=0,0,M29/M34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t>Realized net price per M tokens ($)</t>
         </is>
       </c>
-      <c r="B37" s="26">
-        <f>IF(B10=0,0,B33/B10)</f>
-        <v/>
-      </c>
-      <c r="C37" s="26">
-        <f>IF(C10=0,0,C33/C10)</f>
-        <v/>
-      </c>
-      <c r="D37" s="26">
-        <f>IF(D10=0,0,D33/D10)</f>
-        <v/>
-      </c>
-      <c r="E37" s="26">
-        <f>IF(E10=0,0,E33/E10)</f>
-        <v/>
-      </c>
-      <c r="F37" s="26">
-        <f>IF(F10=0,0,F33/F10)</f>
-        <v/>
-      </c>
-      <c r="G37" s="26">
-        <f>IF(G10=0,0,G33/G10)</f>
-        <v/>
-      </c>
-      <c r="H37" s="26">
-        <f>IF(H10=0,0,H33/H10)</f>
-        <v/>
-      </c>
-      <c r="I37" s="26">
-        <f>IF(I10=0,0,I33/I10)</f>
-        <v/>
-      </c>
-      <c r="J37" s="26">
-        <f>IF(J10=0,0,J33/J10)</f>
-        <v/>
-      </c>
-      <c r="K37" s="26">
-        <f>IF(K10=0,0,K33/K10)</f>
-        <v/>
-      </c>
-      <c r="L37" s="26">
-        <f>IF(L10=0,0,L33/L10)</f>
-        <v/>
-      </c>
-      <c r="M37" s="26">
-        <f>IF(M10=0,0,M33/M10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="B38" s="26">
+        <f>IF(B10=0,0,B34/B10)</f>
+        <v/>
+      </c>
+      <c r="C38" s="26">
+        <f>IF(C10=0,0,C34/C10)</f>
+        <v/>
+      </c>
+      <c r="D38" s="26">
+        <f>IF(D10=0,0,D34/D10)</f>
+        <v/>
+      </c>
+      <c r="E38" s="26">
+        <f>IF(E10=0,0,E34/E10)</f>
+        <v/>
+      </c>
+      <c r="F38" s="26">
+        <f>IF(F10=0,0,F34/F10)</f>
+        <v/>
+      </c>
+      <c r="G38" s="26">
+        <f>IF(G10=0,0,G34/G10)</f>
+        <v/>
+      </c>
+      <c r="H38" s="26">
+        <f>IF(H10=0,0,H34/H10)</f>
+        <v/>
+      </c>
+      <c r="I38" s="26">
+        <f>IF(I10=0,0,I34/I10)</f>
+        <v/>
+      </c>
+      <c r="J38" s="26">
+        <f>IF(J10=0,0,J34/J10)</f>
+        <v/>
+      </c>
+      <c r="K38" s="26">
+        <f>IF(K10=0,0,K34/K10)</f>
+        <v/>
+      </c>
+      <c r="L38" s="26">
+        <f>IF(L10=0,0,L34/L10)</f>
+        <v/>
+      </c>
+      <c r="M38" s="26">
+        <f>IF(M10=0,0,M34/M10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Other lines</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="20" t="n"/>
-      <c r="D39" s="20" t="n"/>
-      <c r="E39" s="20" t="n"/>
-      <c r="F39" s="20" t="n"/>
-      <c r="G39" s="20" t="n"/>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="20" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="20" t="n"/>
-      <c r="L39" s="20" t="n"/>
-      <c r="M39" s="20" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>List value of tokens ($k)</t>
-        </is>
-      </c>
-      <c r="B40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,B$4)/1000</f>
-        <v/>
-      </c>
-      <c r="C40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,C$4)/1000</f>
-        <v/>
-      </c>
-      <c r="D40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,D$4)/1000</f>
-        <v/>
-      </c>
-      <c r="E40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,E$4)/1000</f>
-        <v/>
-      </c>
-      <c r="F40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,F$4)/1000</f>
-        <v/>
-      </c>
-      <c r="G40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,G$4)/1000</f>
-        <v/>
-      </c>
-      <c r="H40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,H$4)/1000</f>
-        <v/>
-      </c>
-      <c r="I40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,I$4)/1000</f>
-        <v/>
-      </c>
-      <c r="J40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,J$4)/1000</f>
-        <v/>
-      </c>
-      <c r="K40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,K$4)/1000</f>
-        <v/>
-      </c>
-      <c r="L40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,L$4)/1000</f>
-        <v/>
-      </c>
-      <c r="M40" s="21">
-        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,M$4)/1000</f>
-        <v/>
-      </c>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+      <c r="L40" s="20" t="n"/>
+      <c r="M40" s="20" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Free credit used ($k)</t>
-        </is>
-      </c>
-      <c r="B41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,B$4)/1000</f>
-        <v/>
-      </c>
-      <c r="C41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,C$4)/1000</f>
-        <v/>
-      </c>
-      <c r="D41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,D$4)/1000</f>
-        <v/>
-      </c>
-      <c r="E41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,E$4)/1000</f>
-        <v/>
-      </c>
-      <c r="F41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,F$4)/1000</f>
-        <v/>
-      </c>
-      <c r="G41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,G$4)/1000</f>
-        <v/>
-      </c>
-      <c r="H41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,H$4)/1000</f>
-        <v/>
-      </c>
-      <c r="I41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,I$4)/1000</f>
-        <v/>
-      </c>
-      <c r="J41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,J$4)/1000</f>
-        <v/>
-      </c>
-      <c r="K41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,K$4)/1000</f>
-        <v/>
-      </c>
-      <c r="L41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,L$4)/1000</f>
-        <v/>
-      </c>
-      <c r="M41" s="24">
-        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,M$4)/1000</f>
+          <t>List value of tokens ($k)</t>
+        </is>
+      </c>
+      <c r="B41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,B$4)/1000</f>
+        <v/>
+      </c>
+      <c r="C41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,C$4)/1000</f>
+        <v/>
+      </c>
+      <c r="D41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,D$4)/1000</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,E$4)/1000</f>
+        <v/>
+      </c>
+      <c r="F41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,F$4)/1000</f>
+        <v/>
+      </c>
+      <c r="G41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,G$4)/1000</f>
+        <v/>
+      </c>
+      <c r="H41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,H$4)/1000</f>
+        <v/>
+      </c>
+      <c r="I41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,I$4)/1000</f>
+        <v/>
+      </c>
+      <c r="J41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,J$4)/1000</f>
+        <v/>
+      </c>
+      <c r="K41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,K$4)/1000</f>
+        <v/>
+      </c>
+      <c r="L41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,L$4)/1000</f>
+        <v/>
+      </c>
+      <c r="M41" s="21">
+        <f>SUMIFS(Data_Monthly!$I:$I,Data_Monthly!$A:$A,M$4)/1000</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Gateway fees ($k)</t>
-        </is>
-      </c>
-      <c r="B42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,B$4)/1000</f>
-        <v/>
-      </c>
-      <c r="C42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,C$4)/1000</f>
-        <v/>
-      </c>
-      <c r="D42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,D$4)/1000</f>
-        <v/>
-      </c>
-      <c r="E42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,E$4)/1000</f>
-        <v/>
-      </c>
-      <c r="F42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,F$4)/1000</f>
-        <v/>
-      </c>
-      <c r="G42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,G$4)/1000</f>
-        <v/>
-      </c>
-      <c r="H42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,H$4)/1000</f>
-        <v/>
-      </c>
-      <c r="I42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,I$4)/1000</f>
-        <v/>
-      </c>
-      <c r="J42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,J$4)/1000</f>
-        <v/>
-      </c>
-      <c r="K42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,K$4)/1000</f>
-        <v/>
-      </c>
-      <c r="L42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,L$4)/1000</f>
-        <v/>
-      </c>
-      <c r="M42" s="21">
-        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,M$4)/1000</f>
+          <t>Free credit used ($k)</t>
+        </is>
+      </c>
+      <c r="B42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,B$4)/1000</f>
+        <v/>
+      </c>
+      <c r="C42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,C$4)/1000</f>
+        <v/>
+      </c>
+      <c r="D42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,D$4)/1000</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,E$4)/1000</f>
+        <v/>
+      </c>
+      <c r="F42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,F$4)/1000</f>
+        <v/>
+      </c>
+      <c r="G42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,G$4)/1000</f>
+        <v/>
+      </c>
+      <c r="H42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,H$4)/1000</f>
+        <v/>
+      </c>
+      <c r="I42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,I$4)/1000</f>
+        <v/>
+      </c>
+      <c r="J42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,J$4)/1000</f>
+        <v/>
+      </c>
+      <c r="K42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,K$4)/1000</f>
+        <v/>
+      </c>
+      <c r="L42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,L$4)/1000</f>
+        <v/>
+      </c>
+      <c r="M42" s="24">
+        <f>SUMIFS(Data_Monthly!$H:$H,Data_Monthly!$A:$A,M$4)/1000</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Active accounts (gateways counted once)</t>
-        </is>
-      </c>
-      <c r="B43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,B$4)</f>
-        <v/>
-      </c>
-      <c r="C43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,C$4)</f>
-        <v/>
-      </c>
-      <c r="D43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,D$4)</f>
-        <v/>
-      </c>
-      <c r="E43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,E$4)</f>
-        <v/>
-      </c>
-      <c r="F43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,F$4)</f>
-        <v/>
-      </c>
-      <c r="G43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,G$4)</f>
-        <v/>
-      </c>
-      <c r="H43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,H$4)</f>
-        <v/>
-      </c>
-      <c r="I43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,I$4)</f>
-        <v/>
-      </c>
-      <c r="J43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,J$4)</f>
-        <v/>
-      </c>
-      <c r="K43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,K$4)</f>
-        <v/>
-      </c>
-      <c r="L43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,L$4)</f>
-        <v/>
-      </c>
-      <c r="M43" s="23">
-        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,M$4)</f>
+          <t>Gateway fees ($k)</t>
+        </is>
+      </c>
+      <c r="B43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,B$4)/1000</f>
+        <v/>
+      </c>
+      <c r="C43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,C$4)/1000</f>
+        <v/>
+      </c>
+      <c r="D43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,D$4)/1000</f>
+        <v/>
+      </c>
+      <c r="E43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,E$4)/1000</f>
+        <v/>
+      </c>
+      <c r="F43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,F$4)/1000</f>
+        <v/>
+      </c>
+      <c r="G43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,G$4)/1000</f>
+        <v/>
+      </c>
+      <c r="H43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,H$4)/1000</f>
+        <v/>
+      </c>
+      <c r="I43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,I$4)/1000</f>
+        <v/>
+      </c>
+      <c r="J43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,J$4)/1000</f>
+        <v/>
+      </c>
+      <c r="K43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,K$4)/1000</f>
+        <v/>
+      </c>
+      <c r="L43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,L$4)/1000</f>
+        <v/>
+      </c>
+      <c r="M43" s="21">
+        <f>SUMIFS(Data_Monthly!$M:$M,Data_Monthly!$A:$A,M$4)/1000</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Paying accounts</t>
+          <t>Active accounts (gateways counted once)</t>
         </is>
       </c>
       <c r="B44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,B$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,B$4)</f>
         <v/>
       </c>
       <c r="C44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,C$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,C$4)</f>
         <v/>
       </c>
       <c r="D44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,D$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,D$4)</f>
         <v/>
       </c>
       <c r="E44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,E$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,E$4)</f>
         <v/>
       </c>
       <c r="F44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,F$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,F$4)</f>
         <v/>
       </c>
       <c r="G44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,G$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,G$4)</f>
         <v/>
       </c>
       <c r="H44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,H$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,H$4)</f>
         <v/>
       </c>
       <c r="I44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,I$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,I$4)</f>
         <v/>
       </c>
       <c r="J44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,J$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,J$4)</f>
         <v/>
       </c>
       <c r="K44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,K$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,K$4)</f>
         <v/>
       </c>
       <c r="L44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,L$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,L$4)</f>
         <v/>
       </c>
       <c r="M44" s="23">
-        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,M$4)</f>
+        <f>SUMIFS(Data_Monthly!$D:$D,Data_Monthly!$A:$A,M$4)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>Paying accounts</t>
+        </is>
+      </c>
+      <c r="B45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,B$4)</f>
+        <v/>
+      </c>
+      <c r="C45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,C$4)</f>
+        <v/>
+      </c>
+      <c r="D45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,D$4)</f>
+        <v/>
+      </c>
+      <c r="E45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,E$4)</f>
+        <v/>
+      </c>
+      <c r="F45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,F$4)</f>
+        <v/>
+      </c>
+      <c r="G45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,G$4)</f>
+        <v/>
+      </c>
+      <c r="H45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,H$4)</f>
+        <v/>
+      </c>
+      <c r="I45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,I$4)</f>
+        <v/>
+      </c>
+      <c r="J45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,J$4)</f>
+        <v/>
+      </c>
+      <c r="K45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,K$4)</f>
+        <v/>
+      </c>
+      <c r="L45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,L$4)</f>
+        <v/>
+      </c>
+      <c r="M45" s="23">
+        <f>SUMIFS(Data_Monthly!$E:$E,Data_Monthly!$A:$A,M$4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>Failed calls as % of all calls (not billed)</t>
         </is>
       </c>
-      <c r="B45" s="25">
+      <c r="B46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,B$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,B$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,B$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,B$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,B$4)))</f>
         <v/>
       </c>
-      <c r="C45" s="25">
+      <c r="C46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,C$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,C$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,C$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,C$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,C$4)))</f>
         <v/>
       </c>
-      <c r="D45" s="25">
+      <c r="D46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,D$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,D$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,D$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,D$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,D$4)))</f>
         <v/>
       </c>
-      <c r="E45" s="25">
+      <c r="E46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,E$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,E$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,E$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,E$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,E$4)))</f>
         <v/>
       </c>
-      <c r="F45" s="25">
+      <c r="F46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,F$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,F$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,F$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,F$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,F$4)))</f>
         <v/>
       </c>
-      <c r="G45" s="25">
+      <c r="G46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,G$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,G$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,G$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,G$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,G$4)))</f>
         <v/>
       </c>
-      <c r="H45" s="25">
+      <c r="H46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,H$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,H$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,H$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,H$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,H$4)))</f>
         <v/>
       </c>
-      <c r="I45" s="25">
+      <c r="I46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,I$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,I$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,I$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,I$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,I$4)))</f>
         <v/>
       </c>
-      <c r="J45" s="25">
+      <c r="J46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,J$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,J$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,J$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,J$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,J$4)))</f>
         <v/>
       </c>
-      <c r="K45" s="25">
+      <c r="K46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,K$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,K$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,K$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,K$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,K$4)))</f>
         <v/>
       </c>
-      <c r="L45" s="25">
+      <c r="L46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,L$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,L$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,L$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,L$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,L$4)))</f>
         <v/>
       </c>
-      <c r="M45" s="25">
+      <c r="M46" s="25">
         <f>IF(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,M$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,M$4)=0,0,SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,M$4)/(SUMIFS(Data_Reliability!$B:$B,Data_Reliability!$A:$A,M$4)+SUMIFS(Data_Reliability!$C:$C,Data_Reliability!$A:$A,M$4)))</f>
         <v/>
       </c>
@@ -27383,7 +28975,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Self-serve by cohort (chain-ladder) + gateway trend + enterprise contracts and pipeline (Forecast_Ent). Blue cells are judgment inputs, seeded from config.</t>
+          <t>Self-serve by cohort (chain-ladder) + gateway trend + enterprise contracts and pipeline (Forecast_Ent). Green input cells link to the Overrides tab, where the values are set.</t>
         </is>
       </c>
     </row>
@@ -27428,14 +29020,17 @@
           <t>Cohort development factor beyond observed history</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>1</v>
+      <c r="B6" s="34">
+        <f>Overrides!$E$8</f>
+        <v/>
+      </c>
+      <c r="C6" s="35">
+        <f>Overrides!$E$9</f>
+        <v/>
+      </c>
+      <c r="D6" s="34">
+        <f>Overrides!$E$10</f>
+        <v/>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -27449,8 +29044,9 @@
           <t>New signups, monthly growth</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n">
-        <v>0</v>
+      <c r="B7" s="11">
+        <f>Overrides!$E$17</f>
+        <v/>
       </c>
       <c r="C7" s="25">
         <f>IF(AND(B29&gt;0,B32&gt;0),(B32/B29)^(1/3)-1,0)</f>
@@ -27472,15 +29068,15 @@
           <t>Month-0 tokens/day per signup (B)</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="36">
         <f>IF(COUNT(C30:C32)=0,0,MIN(C30:C32))</f>
         <v/>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="36">
         <f>IF(COUNT(C30:C32)=0,0,AVERAGE(C30:C32))</f>
         <v/>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="36">
         <f>IF(COUNT(C30:C32)=0,0,MAX(C30:C32))</f>
         <v/>
       </c>
@@ -27520,8 +29116,9 @@
           <t>Gateway growth decay (base)</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n">
-        <v>0.5</v>
+      <c r="C10" s="35">
+        <f>Overrides!$E$18</f>
+        <v/>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -27535,14 +29132,17 @@
           <t>Enterprise steady-state usage vs commitment</t>
         </is>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C11" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>1.2</v>
+      <c r="B11" s="11">
+        <f>Overrides!$E$11</f>
+        <v/>
+      </c>
+      <c r="C11" s="37">
+        <f>Overrides!$E$12</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>Overrides!$E$13</f>
+        <v/>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -27556,14 +29156,17 @@
           <t>Enterprise monthly growth after ramp</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>0.06</v>
+      <c r="B12" s="11">
+        <f>Overrides!$E$14</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>Overrides!$E$15</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>Overrides!$E$16</f>
+        <v/>
       </c>
       <c r="E12" s="7" t="inlineStr"/>
     </row>
@@ -27573,8 +29176,9 @@
           <t>Enterprise ramp length (days)</t>
         </is>
       </c>
-      <c r="C13" s="39" t="n">
-        <v>60</v>
+      <c r="C13" s="12">
+        <f>Overrides!$E$19</f>
+        <v/>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -27589,7 +29193,7 @@
         </is>
       </c>
       <c r="C14" s="13">
-        <f>IF(Monthly!M7=0,0,Monthly!M30/Monthly!M7)</f>
+        <f>Overrides!$E$20</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -27605,7 +29209,7 @@
         </is>
       </c>
       <c r="C15" s="13">
-        <f>IF(Monthly!M8=0,0,Monthly!M31/Monthly!M8)</f>
+        <f>Overrides!$E$21</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -27721,7 +29325,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A21)</f>
         <v/>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="36">
         <f>IF(B21&gt;0,D21/B21,"")</f>
         <v/>
       </c>
@@ -27783,7 +29387,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A22)</f>
         <v/>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="36">
         <f>IF(B22&gt;0,D22/B22,"")</f>
         <v/>
       </c>
@@ -27841,7 +29445,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A23)</f>
         <v/>
       </c>
-      <c r="C23" s="37">
+      <c r="C23" s="36">
         <f>IF(B23&gt;0,D23/B23,"")</f>
         <v/>
       </c>
@@ -27895,7 +29499,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A24)</f>
         <v/>
       </c>
-      <c r="C24" s="37">
+      <c r="C24" s="36">
         <f>IF(B24&gt;0,D24/B24,"")</f>
         <v/>
       </c>
@@ -27945,7 +29549,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A25)</f>
         <v/>
       </c>
-      <c r="C25" s="37">
+      <c r="C25" s="36">
         <f>IF(B25&gt;0,D25/B25,"")</f>
         <v/>
       </c>
@@ -27991,7 +29595,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A26)</f>
         <v/>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="36">
         <f>IF(B26&gt;0,D26/B26,"")</f>
         <v/>
       </c>
@@ -28033,7 +29637,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A27)</f>
         <v/>
       </c>
-      <c r="C27" s="37">
+      <c r="C27" s="36">
         <f>IF(B27&gt;0,D27/B27,"")</f>
         <v/>
       </c>
@@ -28071,7 +29675,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A28)</f>
         <v/>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="36">
         <f>IF(B28&gt;0,D28/B28,"")</f>
         <v/>
       </c>
@@ -28105,7 +29709,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A29)</f>
         <v/>
       </c>
-      <c r="C29" s="37">
+      <c r="C29" s="36">
         <f>IF(B29&gt;0,D29/B29,"")</f>
         <v/>
       </c>
@@ -28135,7 +29739,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A30)</f>
         <v/>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="36">
         <f>IF(B30&gt;0,D30/B30,"")</f>
         <v/>
       </c>
@@ -28161,7 +29765,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A31)</f>
         <v/>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="36">
         <f>IF(B31&gt;0,D31/B31,"")</f>
         <v/>
       </c>
@@ -28183,7 +29787,7 @@
         <f>SUMIFS(Data_Signups!$B:$B,Data_Signups!$A:$A,$A32)</f>
         <v/>
       </c>
-      <c r="C32" s="37">
+      <c r="C32" s="36">
         <f>IF(B32&gt;0,D32/B32,"")</f>
         <v/>
       </c>
@@ -28269,47 +29873,47 @@
         <f>A21</f>
         <v/>
       </c>
-      <c r="D36" s="40">
+      <c r="D36" s="38">
         <f>IF(D21&gt;0,E21/D21,"")</f>
         <v/>
       </c>
-      <c r="E36" s="40">
+      <c r="E36" s="38">
         <f>IF(E21&gt;0,F21/E21,"")</f>
         <v/>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="38">
         <f>IF(F21&gt;0,G21/F21,"")</f>
         <v/>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="38">
         <f>IF(G21&gt;0,H21/G21,"")</f>
         <v/>
       </c>
-      <c r="H36" s="40">
+      <c r="H36" s="38">
         <f>IF(H21&gt;0,I21/H21,"")</f>
         <v/>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="38">
         <f>IF(I21&gt;0,J21/I21,"")</f>
         <v/>
       </c>
-      <c r="J36" s="40">
+      <c r="J36" s="38">
         <f>IF(J21&gt;0,K21/J21,"")</f>
         <v/>
       </c>
-      <c r="K36" s="40">
+      <c r="K36" s="38">
         <f>IF(K21&gt;0,L21/K21,"")</f>
         <v/>
       </c>
-      <c r="L36" s="40">
+      <c r="L36" s="38">
         <f>IF(L21&gt;0,M21/L21,"")</f>
         <v/>
       </c>
-      <c r="M36" s="40">
+      <c r="M36" s="38">
         <f>IF(M21&gt;0,N21/M21,"")</f>
         <v/>
       </c>
-      <c r="N36" s="40">
+      <c r="N36" s="38">
         <f>IF(N21&gt;0,O21/N21,"")</f>
         <v/>
       </c>
@@ -28319,43 +29923,43 @@
         <f>A22</f>
         <v/>
       </c>
-      <c r="D37" s="40">
+      <c r="D37" s="38">
         <f>IF(D22&gt;0,E22/D22,"")</f>
         <v/>
       </c>
-      <c r="E37" s="40">
+      <c r="E37" s="38">
         <f>IF(E22&gt;0,F22/E22,"")</f>
         <v/>
       </c>
-      <c r="F37" s="40">
+      <c r="F37" s="38">
         <f>IF(F22&gt;0,G22/F22,"")</f>
         <v/>
       </c>
-      <c r="G37" s="40">
+      <c r="G37" s="38">
         <f>IF(G22&gt;0,H22/G22,"")</f>
         <v/>
       </c>
-      <c r="H37" s="40">
+      <c r="H37" s="38">
         <f>IF(H22&gt;0,I22/H22,"")</f>
         <v/>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="38">
         <f>IF(I22&gt;0,J22/I22,"")</f>
         <v/>
       </c>
-      <c r="J37" s="40">
+      <c r="J37" s="38">
         <f>IF(J22&gt;0,K22/J22,"")</f>
         <v/>
       </c>
-      <c r="K37" s="40">
+      <c r="K37" s="38">
         <f>IF(K22&gt;0,L22/K22,"")</f>
         <v/>
       </c>
-      <c r="L37" s="40">
+      <c r="L37" s="38">
         <f>IF(L22&gt;0,M22/L22,"")</f>
         <v/>
       </c>
-      <c r="M37" s="40">
+      <c r="M37" s="38">
         <f>IF(M22&gt;0,N22/M22,"")</f>
         <v/>
       </c>
@@ -28365,39 +29969,39 @@
         <f>A23</f>
         <v/>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="38">
         <f>IF(D23&gt;0,E23/D23,"")</f>
         <v/>
       </c>
-      <c r="E38" s="40">
+      <c r="E38" s="38">
         <f>IF(E23&gt;0,F23/E23,"")</f>
         <v/>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="38">
         <f>IF(F23&gt;0,G23/F23,"")</f>
         <v/>
       </c>
-      <c r="G38" s="40">
+      <c r="G38" s="38">
         <f>IF(G23&gt;0,H23/G23,"")</f>
         <v/>
       </c>
-      <c r="H38" s="40">
+      <c r="H38" s="38">
         <f>IF(H23&gt;0,I23/H23,"")</f>
         <v/>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="38">
         <f>IF(I23&gt;0,J23/I23,"")</f>
         <v/>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="38">
         <f>IF(J23&gt;0,K23/J23,"")</f>
         <v/>
       </c>
-      <c r="K38" s="40">
+      <c r="K38" s="38">
         <f>IF(K23&gt;0,L23/K23,"")</f>
         <v/>
       </c>
-      <c r="L38" s="40">
+      <c r="L38" s="38">
         <f>IF(L23&gt;0,M23/L23,"")</f>
         <v/>
       </c>
@@ -28407,35 +30011,35 @@
         <f>A24</f>
         <v/>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="38">
         <f>IF(D24&gt;0,E24/D24,"")</f>
         <v/>
       </c>
-      <c r="E39" s="40">
+      <c r="E39" s="38">
         <f>IF(E24&gt;0,F24/E24,"")</f>
         <v/>
       </c>
-      <c r="F39" s="40">
+      <c r="F39" s="38">
         <f>IF(F24&gt;0,G24/F24,"")</f>
         <v/>
       </c>
-      <c r="G39" s="40">
+      <c r="G39" s="38">
         <f>IF(G24&gt;0,H24/G24,"")</f>
         <v/>
       </c>
-      <c r="H39" s="40">
+      <c r="H39" s="38">
         <f>IF(H24&gt;0,I24/H24,"")</f>
         <v/>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="38">
         <f>IF(I24&gt;0,J24/I24,"")</f>
         <v/>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="38">
         <f>IF(J24&gt;0,K24/J24,"")</f>
         <v/>
       </c>
-      <c r="K39" s="40">
+      <c r="K39" s="38">
         <f>IF(K24&gt;0,L24/K24,"")</f>
         <v/>
       </c>
@@ -28445,31 +30049,31 @@
         <f>A25</f>
         <v/>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="38">
         <f>IF(D25&gt;0,E25/D25,"")</f>
         <v/>
       </c>
-      <c r="E40" s="40">
+      <c r="E40" s="38">
         <f>IF(E25&gt;0,F25/E25,"")</f>
         <v/>
       </c>
-      <c r="F40" s="40">
+      <c r="F40" s="38">
         <f>IF(F25&gt;0,G25/F25,"")</f>
         <v/>
       </c>
-      <c r="G40" s="40">
+      <c r="G40" s="38">
         <f>IF(G25&gt;0,H25/G25,"")</f>
         <v/>
       </c>
-      <c r="H40" s="40">
+      <c r="H40" s="38">
         <f>IF(H25&gt;0,I25/H25,"")</f>
         <v/>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="38">
         <f>IF(I25&gt;0,J25/I25,"")</f>
         <v/>
       </c>
-      <c r="J40" s="40">
+      <c r="J40" s="38">
         <f>IF(J25&gt;0,K25/J25,"")</f>
         <v/>
       </c>
@@ -28479,27 +30083,27 @@
         <f>A26</f>
         <v/>
       </c>
-      <c r="D41" s="40">
+      <c r="D41" s="38">
         <f>IF(D26&gt;0,E26/D26,"")</f>
         <v/>
       </c>
-      <c r="E41" s="40">
+      <c r="E41" s="38">
         <f>IF(E26&gt;0,F26/E26,"")</f>
         <v/>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="38">
         <f>IF(F26&gt;0,G26/F26,"")</f>
         <v/>
       </c>
-      <c r="G41" s="40">
+      <c r="G41" s="38">
         <f>IF(G26&gt;0,H26/G26,"")</f>
         <v/>
       </c>
-      <c r="H41" s="40">
+      <c r="H41" s="38">
         <f>IF(H26&gt;0,I26/H26,"")</f>
         <v/>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="38">
         <f>IF(I26&gt;0,J26/I26,"")</f>
         <v/>
       </c>
@@ -28509,23 +30113,23 @@
         <f>A27</f>
         <v/>
       </c>
-      <c r="D42" s="40">
+      <c r="D42" s="38">
         <f>IF(D27&gt;0,E27/D27,"")</f>
         <v/>
       </c>
-      <c r="E42" s="40">
+      <c r="E42" s="38">
         <f>IF(E27&gt;0,F27/E27,"")</f>
         <v/>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="38">
         <f>IF(F27&gt;0,G27/F27,"")</f>
         <v/>
       </c>
-      <c r="G42" s="40">
+      <c r="G42" s="38">
         <f>IF(G27&gt;0,H27/G27,"")</f>
         <v/>
       </c>
-      <c r="H42" s="40">
+      <c r="H42" s="38">
         <f>IF(H27&gt;0,I27/H27,"")</f>
         <v/>
       </c>
@@ -28535,19 +30139,19 @@
         <f>A28</f>
         <v/>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="38">
         <f>IF(D28&gt;0,E28/D28,"")</f>
         <v/>
       </c>
-      <c r="E43" s="40">
+      <c r="E43" s="38">
         <f>IF(E28&gt;0,F28/E28,"")</f>
         <v/>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="38">
         <f>IF(F28&gt;0,G28/F28,"")</f>
         <v/>
       </c>
-      <c r="G43" s="40">
+      <c r="G43" s="38">
         <f>IF(G28&gt;0,H28/G28,"")</f>
         <v/>
       </c>
@@ -28557,15 +30161,15 @@
         <f>A29</f>
         <v/>
       </c>
-      <c r="D44" s="40">
+      <c r="D44" s="38">
         <f>IF(D29&gt;0,E29/D29,"")</f>
         <v/>
       </c>
-      <c r="E44" s="40">
+      <c r="E44" s="38">
         <f>IF(E29&gt;0,F29/E29,"")</f>
         <v/>
       </c>
-      <c r="F44" s="40">
+      <c r="F44" s="38">
         <f>IF(F29&gt;0,G29/F29,"")</f>
         <v/>
       </c>
@@ -28575,11 +30179,11 @@
         <f>A30</f>
         <v/>
       </c>
-      <c r="D45" s="40">
+      <c r="D45" s="38">
         <f>IF(D30&gt;0,E30/D30,"")</f>
         <v/>
       </c>
-      <c r="E45" s="40">
+      <c r="E45" s="38">
         <f>IF(E30&gt;0,F30/E30,"")</f>
         <v/>
       </c>
@@ -28589,7 +30193,7 @@
         <f>A31</f>
         <v/>
       </c>
-      <c r="D46" s="40">
+      <c r="D46" s="38">
         <f>IF(D31&gt;0,E31/D31,"")</f>
         <v/>
       </c>
@@ -29327,59 +30931,59 @@
           <t>Development factor, month k to k+1</t>
         </is>
       </c>
-      <c r="D66" s="40">
+      <c r="D66" s="38">
         <f>IF(COUNT(D36:D46)=0,$B$6,MIN(D36:D46))</f>
         <v/>
       </c>
-      <c r="E66" s="40">
+      <c r="E66" s="38">
         <f>IF(COUNT(E36:E45)=0,$B$6,MIN(E36:E45))</f>
         <v/>
       </c>
-      <c r="F66" s="40">
+      <c r="F66" s="38">
         <f>IF(COUNT(F36:F44)=0,$B$6,MIN(F36:F44))</f>
         <v/>
       </c>
-      <c r="G66" s="40">
+      <c r="G66" s="38">
         <f>IF(COUNT(G36:G43)=0,$B$6,MIN(G36:G43))</f>
         <v/>
       </c>
-      <c r="H66" s="40">
+      <c r="H66" s="38">
         <f>IF(COUNT(H36:H42)=0,$B$6,MIN(H36:H42))</f>
         <v/>
       </c>
-      <c r="I66" s="40">
+      <c r="I66" s="38">
         <f>IF(COUNT(I36:I41)=0,$B$6,MIN(I36:I41))</f>
         <v/>
       </c>
-      <c r="J66" s="40">
+      <c r="J66" s="38">
         <f>IF(COUNT(J36:J40)=0,$B$6,MIN(J36:J40))</f>
         <v/>
       </c>
-      <c r="K66" s="40">
+      <c r="K66" s="38">
         <f>IF(COUNT(K36:K39)=0,$B$6,MIN(K36:K39))</f>
         <v/>
       </c>
-      <c r="L66" s="40">
+      <c r="L66" s="38">
         <f>IF(COUNT(L36:L38)=0,$B$6,MIN(L36:L38))</f>
         <v/>
       </c>
-      <c r="M66" s="40">
+      <c r="M66" s="38">
         <f>IF(COUNT(M36:M37)=0,$B$6,MIN(M36:M37))</f>
         <v/>
       </c>
-      <c r="N66" s="40">
+      <c r="N66" s="38">
         <f>IF(COUNT(N36:N36)=0,$B$6,MIN(N36:N36))</f>
         <v/>
       </c>
-      <c r="O66" s="40">
+      <c r="O66" s="38">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="P66" s="40">
+      <c r="P66" s="38">
         <f>$B$6</f>
         <v/>
       </c>
-      <c r="Q66" s="40">
+      <c r="Q66" s="38">
         <f>$B$6</f>
         <v/>
       </c>
@@ -30117,59 +31721,59 @@
           <t>Development factor, month k to k+1</t>
         </is>
       </c>
-      <c r="D86" s="40">
+      <c r="D86" s="38">
         <f>IF(SUM(D21:D31)=0,$C$6,SUMPRODUCT((D21:D31&gt;0)*E21:E31)/SUM(D21:D31))</f>
         <v/>
       </c>
-      <c r="E86" s="40">
+      <c r="E86" s="38">
         <f>IF(SUM(E21:E30)=0,$C$6,SUMPRODUCT((E21:E30&gt;0)*F21:F30)/SUM(E21:E30))</f>
         <v/>
       </c>
-      <c r="F86" s="40">
+      <c r="F86" s="38">
         <f>IF(SUM(F21:F29)=0,$C$6,SUMPRODUCT((F21:F29&gt;0)*G21:G29)/SUM(F21:F29))</f>
         <v/>
       </c>
-      <c r="G86" s="40">
+      <c r="G86" s="38">
         <f>IF(SUM(G21:G28)=0,$C$6,SUMPRODUCT((G21:G28&gt;0)*H21:H28)/SUM(G21:G28))</f>
         <v/>
       </c>
-      <c r="H86" s="40">
+      <c r="H86" s="38">
         <f>IF(SUM(H21:H27)=0,$C$6,SUMPRODUCT((H21:H27&gt;0)*I21:I27)/SUM(H21:H27))</f>
         <v/>
       </c>
-      <c r="I86" s="40">
+      <c r="I86" s="38">
         <f>IF(SUM(I21:I26)=0,$C$6,SUMPRODUCT((I21:I26&gt;0)*J21:J26)/SUM(I21:I26))</f>
         <v/>
       </c>
-      <c r="J86" s="40">
+      <c r="J86" s="38">
         <f>IF(SUM(J21:J25)=0,$C$6,SUMPRODUCT((J21:J25&gt;0)*K21:K25)/SUM(J21:J25))</f>
         <v/>
       </c>
-      <c r="K86" s="40">
+      <c r="K86" s="38">
         <f>IF(SUM(K21:K24)=0,$C$6,SUMPRODUCT((K21:K24&gt;0)*L21:L24)/SUM(K21:K24))</f>
         <v/>
       </c>
-      <c r="L86" s="40">
+      <c r="L86" s="38">
         <f>IF(SUM(L21:L23)=0,$C$6,SUMPRODUCT((L21:L23&gt;0)*M21:M23)/SUM(L21:L23))</f>
         <v/>
       </c>
-      <c r="M86" s="40">
+      <c r="M86" s="38">
         <f>IF(SUM(M21:M22)=0,$C$6,SUMPRODUCT((M21:M22&gt;0)*N21:N22)/SUM(M21:M22))</f>
         <v/>
       </c>
-      <c r="N86" s="40">
+      <c r="N86" s="38">
         <f>IF(SUM(N21:N21)=0,$C$6,SUMPRODUCT((N21:N21&gt;0)*O21:O21)/SUM(N21:N21))</f>
         <v/>
       </c>
-      <c r="O86" s="40">
+      <c r="O86" s="38">
         <f>$C$6</f>
         <v/>
       </c>
-      <c r="P86" s="40">
+      <c r="P86" s="38">
         <f>$C$6</f>
         <v/>
       </c>
-      <c r="Q86" s="40">
+      <c r="Q86" s="38">
         <f>$C$6</f>
         <v/>
       </c>
@@ -30907,59 +32511,59 @@
           <t>Development factor, month k to k+1</t>
         </is>
       </c>
-      <c r="D106" s="40">
+      <c r="D106" s="38">
         <f>IF(COUNT(D36:D46)=0,$D$6,MAX(D36:D46))</f>
         <v/>
       </c>
-      <c r="E106" s="40">
+      <c r="E106" s="38">
         <f>IF(COUNT(E36:E45)=0,$D$6,MAX(E36:E45))</f>
         <v/>
       </c>
-      <c r="F106" s="40">
+      <c r="F106" s="38">
         <f>IF(COUNT(F36:F44)=0,$D$6,MAX(F36:F44))</f>
         <v/>
       </c>
-      <c r="G106" s="40">
+      <c r="G106" s="38">
         <f>IF(COUNT(G36:G43)=0,$D$6,MAX(G36:G43))</f>
         <v/>
       </c>
-      <c r="H106" s="40">
+      <c r="H106" s="38">
         <f>IF(COUNT(H36:H42)=0,$D$6,MAX(H36:H42))</f>
         <v/>
       </c>
-      <c r="I106" s="40">
+      <c r="I106" s="38">
         <f>IF(COUNT(I36:I41)=0,$D$6,MAX(I36:I41))</f>
         <v/>
       </c>
-      <c r="J106" s="40">
+      <c r="J106" s="38">
         <f>IF(COUNT(J36:J40)=0,$D$6,MAX(J36:J40))</f>
         <v/>
       </c>
-      <c r="K106" s="40">
+      <c r="K106" s="38">
         <f>IF(COUNT(K36:K39)=0,$D$6,MAX(K36:K39))</f>
         <v/>
       </c>
-      <c r="L106" s="40">
+      <c r="L106" s="38">
         <f>IF(COUNT(L36:L38)=0,$D$6,MAX(L36:L38))</f>
         <v/>
       </c>
-      <c r="M106" s="40">
+      <c r="M106" s="38">
         <f>IF(COUNT(M36:M37)=0,$D$6,MAX(M36:M37))</f>
         <v/>
       </c>
-      <c r="N106" s="40">
+      <c r="N106" s="38">
         <f>IF(COUNT(N36:N36)=0,$D$6,MAX(N36:N36))</f>
         <v/>
       </c>
-      <c r="O106" s="40">
+      <c r="O106" s="38">
         <f>$D$6</f>
         <v/>
       </c>
-      <c r="P106" s="40">
+      <c r="P106" s="38">
         <f>$D$6</f>
         <v/>
       </c>
-      <c r="Q106" s="40">
+      <c r="Q106" s="38">
         <f>$D$6</f>
         <v/>
       </c>
@@ -31118,51 +32722,51 @@
           <t>Actual</t>
         </is>
       </c>
-      <c r="B117" s="41">
+      <c r="B117" s="39">
         <f>Monthly!B15</f>
         <v/>
       </c>
-      <c r="C117" s="41">
+      <c r="C117" s="39">
         <f>Monthly!C15</f>
         <v/>
       </c>
-      <c r="D117" s="41">
+      <c r="D117" s="39">
         <f>Monthly!D15</f>
         <v/>
       </c>
-      <c r="E117" s="41">
+      <c r="E117" s="39">
         <f>Monthly!E15</f>
         <v/>
       </c>
-      <c r="F117" s="41">
+      <c r="F117" s="39">
         <f>Monthly!F15</f>
         <v/>
       </c>
-      <c r="G117" s="41">
+      <c r="G117" s="39">
         <f>Monthly!G15</f>
         <v/>
       </c>
-      <c r="H117" s="41">
+      <c r="H117" s="39">
         <f>Monthly!H15</f>
         <v/>
       </c>
-      <c r="I117" s="41">
+      <c r="I117" s="39">
         <f>Monthly!I15</f>
         <v/>
       </c>
-      <c r="J117" s="41">
+      <c r="J117" s="39">
         <f>Monthly!J15</f>
         <v/>
       </c>
-      <c r="K117" s="41">
+      <c r="K117" s="39">
         <f>Monthly!K15</f>
         <v/>
       </c>
-      <c r="L117" s="41">
+      <c r="L117" s="39">
         <f>Monthly!L15</f>
         <v/>
       </c>
-      <c r="M117" s="41">
+      <c r="M117" s="39">
         <f>Monthly!M15</f>
         <v/>
       </c>
@@ -31181,7 +32785,7 @@
     <row r="119"/>
     <row r="120"/>
     <row r="121">
-      <c r="A121" s="42" t="inlineStr">
+      <c r="A121" s="40" t="inlineStr">
         <is>
           <t>FORECAST SUMMARY</t>
         </is>
@@ -31322,39 +32926,39 @@
           <t>Enterprise, signed contracts</t>
         </is>
       </c>
-      <c r="B125" s="41">
+      <c r="B125" s="39">
         <f>Forecast_Ent!K53</f>
         <v/>
       </c>
-      <c r="C125" s="41">
+      <c r="C125" s="39">
         <f>Forecast_Ent!L53</f>
         <v/>
       </c>
-      <c r="D125" s="41">
+      <c r="D125" s="39">
         <f>Forecast_Ent!M53</f>
         <v/>
       </c>
-      <c r="E125" s="41">
+      <c r="E125" s="39">
         <f>Forecast_Ent!N53</f>
         <v/>
       </c>
-      <c r="F125" s="41">
+      <c r="F125" s="39">
         <f>Forecast_Ent!O53</f>
         <v/>
       </c>
-      <c r="G125" s="41">
+      <c r="G125" s="39">
         <f>Forecast_Ent!P53</f>
         <v/>
       </c>
-      <c r="H125" s="41">
+      <c r="H125" s="39">
         <f>Forecast_Ent!Q53</f>
         <v/>
       </c>
-      <c r="I125" s="41">
+      <c r="I125" s="39">
         <f>Forecast_Ent!R53</f>
         <v/>
       </c>
-      <c r="J125" s="41">
+      <c r="J125" s="39">
         <f>Forecast_Ent!S53</f>
         <v/>
       </c>
@@ -31365,39 +32969,39 @@
           <t>Enterprise, pipeline</t>
         </is>
       </c>
-      <c r="B126" s="41">
+      <c r="B126" s="39">
         <f>Forecast_Ent!B144</f>
         <v/>
       </c>
-      <c r="C126" s="41">
+      <c r="C126" s="39">
         <f>Forecast_Ent!C144</f>
         <v/>
       </c>
-      <c r="D126" s="41">
+      <c r="D126" s="39">
         <f>Forecast_Ent!D144</f>
         <v/>
       </c>
-      <c r="E126" s="41">
+      <c r="E126" s="39">
         <f>Forecast_Ent!E144</f>
         <v/>
       </c>
-      <c r="F126" s="41">
+      <c r="F126" s="39">
         <f>Forecast_Ent!F144</f>
         <v/>
       </c>
-      <c r="G126" s="41">
+      <c r="G126" s="39">
         <f>Forecast_Ent!G144</f>
         <v/>
       </c>
-      <c r="H126" s="41">
+      <c r="H126" s="39">
         <f>Forecast_Ent!H144</f>
         <v/>
       </c>
-      <c r="I126" s="41">
+      <c r="I126" s="39">
         <f>Forecast_Ent!I144</f>
         <v/>
       </c>
-      <c r="J126" s="41">
+      <c r="J126" s="39">
         <f>Forecast_Ent!J144</f>
         <v/>
       </c>
@@ -31408,39 +33012,39 @@
           <t>Total tokens per day (B)</t>
         </is>
       </c>
-      <c r="B127" s="43">
+      <c r="B127" s="41">
         <f>SUM(B123:B126)</f>
         <v/>
       </c>
-      <c r="C127" s="43">
+      <c r="C127" s="41">
         <f>SUM(C123:C126)</f>
         <v/>
       </c>
-      <c r="D127" s="43">
+      <c r="D127" s="41">
         <f>SUM(D123:D126)</f>
         <v/>
       </c>
-      <c r="E127" s="43">
+      <c r="E127" s="41">
         <f>SUM(E123:E126)</f>
         <v/>
       </c>
-      <c r="F127" s="43">
+      <c r="F127" s="41">
         <f>SUM(F123:F126)</f>
         <v/>
       </c>
-      <c r="G127" s="43">
+      <c r="G127" s="41">
         <f>SUM(G123:G126)</f>
         <v/>
       </c>
-      <c r="H127" s="43">
+      <c r="H127" s="41">
         <f>SUM(H123:H126)</f>
         <v/>
       </c>
-      <c r="I127" s="43">
+      <c r="I127" s="41">
         <f>SUM(I123:I126)</f>
         <v/>
       </c>
-      <c r="J127" s="43">
+      <c r="J127" s="41">
         <f>SUM(J123:J126)</f>
         <v/>
       </c>
@@ -31798,7 +33402,7 @@
         <f>IF(COUNTIFS(Data_FcHistory!$A:$A,EDATE(Data_Params!$B$2,-1),Data_FcHistory!$B:$B,Data_Params!$B$2,Data_FcHistory!$C:$C,"base",Data_FcHistory!$D:$D,"self_serve")=0,"none on file",SUMIFS(Data_FcHistory!$E:$E,Data_FcHistory!$A:$A,EDATE(Data_Params!$B$2,-1),Data_FcHistory!$B:$B,Data_Params!$B$2,Data_FcHistory!$C:$C,"base",Data_FcHistory!$D:$D,"self_serve"))</f>
         <v/>
       </c>
-      <c r="C140" s="41">
+      <c r="C140" s="39">
         <f>Monthly!M14</f>
         <v/>
       </c>
@@ -31825,7 +33429,7 @@
         <f>IF(COUNTIFS(Data_FcHistory!$A:$A,EDATE(Data_Params!$B$2,-1),Data_FcHistory!$B:$B,Data_Params!$B$2,Data_FcHistory!$C:$C,"base",Data_FcHistory!$D:$D,"gateway_aggregate")=0,"none on file",SUMIFS(Data_FcHistory!$E:$E,Data_FcHistory!$A:$A,EDATE(Data_Params!$B$2,-1),Data_FcHistory!$B:$B,Data_Params!$B$2,Data_FcHistory!$C:$C,"base",Data_FcHistory!$D:$D,"gateway_aggregate"))</f>
         <v/>
       </c>
-      <c r="C141" s="41">
+      <c r="C141" s="39">
         <f>Monthly!M15</f>
         <v/>
       </c>
@@ -31852,7 +33456,7 @@
         <f>IF(COUNTIFS(Data_FcHistory!$A:$A,EDATE(Data_Params!$B$2,-1),Data_FcHistory!$B:$B,Data_Params!$B$2,Data_FcHistory!$C:$C,"base",Data_FcHistory!$D:$D,"enterprise")=0,"none on file",SUMIFS(Data_FcHistory!$E:$E,Data_FcHistory!$A:$A,EDATE(Data_Params!$B$2,-1),Data_FcHistory!$B:$B,Data_Params!$B$2,Data_FcHistory!$C:$C,"base",Data_FcHistory!$D:$D,"enterprise"))</f>
         <v/>
       </c>
-      <c r="C142" s="41">
+      <c r="C142" s="39">
         <f>Monthly!M13</f>
         <v/>
       </c>
@@ -31875,15 +33479,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B143" s="43">
+      <c r="B143" s="41">
         <f>IF(COUNT(B140:B142)=0,"none on file",SUM(B140:B142))</f>
         <v/>
       </c>
-      <c r="C143" s="43">
+      <c r="C143" s="41">
         <f>SUM(C140:C142)</f>
         <v/>
       </c>
-      <c r="D143" s="43">
+      <c r="D143" s="41">
         <f>IF(ISNUMBER(B143),C143-B143,"")</f>
         <v/>
       </c>

--- a/template/Jev_Close_Template.xlsx
+++ b/template/Jev_Close_Template.xlsx
@@ -939,7 +939,7 @@
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>Overrides!$E$22</f>
+        <f>Overrides!$E$25</f>
         <v/>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="B6" s="43">
-        <f>Overrides!$E$23</f>
+        <f>Overrides!$E$26</f>
         <v/>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="B7" s="37">
-        <f>Overrides!$E$24</f>
+        <f>Overrides!$E$27</f>
         <v/>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -9109,12 +9109,12 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>Overrides!$E$25</f>
+        <f>Overrides!$E$28</f>
         <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>From your capacity contract.</t>
+          <t>Market placeholder (Oct 2026, ~32% below on-demand). Replace with the contracted rate.</t>
         </is>
       </c>
     </row>
@@ -9125,12 +9125,12 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>Overrides!$E$26</f>
+        <f>Overrides!$E$29</f>
         <v/>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Same provider tier.</t>
+          <t>Market placeholder (Oct 2026): H100 at specialist GPU clouds. Same provider tier as reserved.</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="B10" s="34">
-        <f>Overrides!$E$27</f>
+        <f>Overrides!$E$30</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="B11" s="34">
-        <f>Overrides!$E$28</f>
+        <f>Overrides!$E$31</f>
         <v/>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -10083,29 +10083,29 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>signup_growth.low</t>
+          <t>competitor_churn.low</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Forecast: new signups monthly growth, low</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="n">
-        <v>0</v>
+          <t>Forecast: Self-serve tokens lost to competitors, per month, low</t>
+        </is>
+      </c>
+      <c r="C17" s="50" t="n">
+        <v>0.03</v>
       </c>
       <c r="D17" s="51" t="n"/>
       <c r="E17" s="27">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D17),D17&gt;=-0.5,D17&lt;=1),D17,C17),C17)</f>
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D17),D17&gt;=0,D17&lt;=0.5),D17,C17),C17)</f>
         <v/>
       </c>
       <c r="F17" s="3">
-        <f>IFERROR(IF(ISBLANK(D17),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D17),"Ignored: error value",IF(NOT(ISNUMBER(D17)),"Ignored: not a number",IF(OR(D17&lt;-0.5,D17&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D17),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D17),"Ignored: error value",IF(NOT(ISNUMBER(D17)),"Ignored: not a number",IF(OR(D17&lt;0,D17&gt;0.5),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>-0.5 to 1</t>
+          <t>0 to 0.5</t>
         </is>
       </c>
       <c r="H17" s="18" t="n"/>
@@ -10113,29 +10113,29 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>gateway_growth_decay</t>
+          <t>competitor_churn.base</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Forecast: gateway growth decay (base)</t>
-        </is>
-      </c>
-      <c r="C18" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D18" s="48" t="n"/>
-      <c r="E18" s="49">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D18),D18&gt;=0,D18&lt;=2),D18,C18),C18)</f>
+          <t>Forecast: Self-serve tokens lost to competitors, per month, base</t>
+        </is>
+      </c>
+      <c r="C18" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="51" t="n"/>
+      <c r="E18" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D18),D18&gt;=0,D18&lt;=0.5),D18,C18),C18)</f>
         <v/>
       </c>
       <c r="F18" s="3">
-        <f>IFERROR(IF(ISBLANK(D18),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D18),"Ignored: error value",IF(NOT(ISNUMBER(D18)),"Ignored: not a number",IF(OR(D18&lt;0,D18&gt;2),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D18),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D18),"Ignored: error value",IF(NOT(ISNUMBER(D18)),"Ignored: not a number",IF(OR(D18&lt;0,D18&gt;0.5),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>0 to 2</t>
+          <t>0 to 0.5</t>
         </is>
       </c>
       <c r="H18" s="18" t="n"/>
@@ -10143,29 +10143,29 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>ent_ramp_days</t>
+          <t>competitor_churn.high</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Forecast: enterprise ramp length (days)</t>
-        </is>
-      </c>
-      <c r="C19" s="52" t="n">
-        <v>60</v>
-      </c>
-      <c r="D19" s="53" t="n"/>
-      <c r="E19" s="44">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D19),D19&gt;=1,D19&lt;=365),D19,C19),C19)</f>
+          <t>Forecast: Self-serve tokens lost to competitors, per month, high</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="51" t="n"/>
+      <c r="E19" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D19),D19&gt;=0,D19&lt;=0.5),D19,C19),C19)</f>
         <v/>
       </c>
       <c r="F19" s="3">
-        <f>IFERROR(IF(ISBLANK(D19),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D19),"Ignored: error value",IF(NOT(ISNUMBER(D19)),"Ignored: not a number",IF(OR(D19&lt;1,D19&gt;365),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D19),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D19),"Ignored: error value",IF(NOT(ISNUMBER(D19)),"Ignored: not a number",IF(OR(D19&lt;0,D19&gt;0.5),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>1 to 365</t>
+          <t>0 to 0.5</t>
         </is>
       </c>
       <c r="H19" s="18" t="n"/>
@@ -10173,30 +10173,29 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>price.self_serve</t>
+          <t>signup_growth.low</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Forecast: self-serve net $ per M tokens (price-change test)</t>
-        </is>
-      </c>
-      <c r="C20" s="26">
-        <f>IF(Monthly!M7=0,0,Monthly!M30/Monthly!M7)</f>
-        <v/>
-      </c>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="55">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D20),D20&gt;=0,D20&lt;=1),D20,C20),C20)</f>
+          <t>Forecast: new signups monthly growth, low</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="51" t="n"/>
+      <c r="E20" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D20),D20&gt;=-0.5,D20&lt;=1),D20,C20),C20)</f>
         <v/>
       </c>
       <c r="F20" s="3">
-        <f>IFERROR(IF(ISBLANK(D20),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D20),"Ignored: error value",IF(NOT(ISNUMBER(D20)),"Ignored: not a number",IF(OR(D20&lt;0,D20&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D20),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D20),"Ignored: error value",IF(NOT(ISNUMBER(D20)),"Ignored: not a number",IF(OR(D20&lt;-0.5,D20&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>-0.5 to 1</t>
         </is>
       </c>
       <c r="H20" s="18" t="n"/>
@@ -10204,30 +10203,29 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>price.gateway</t>
+          <t>gateway_growth_decay</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Forecast: gateway net $ per M tokens (price-change test)</t>
-        </is>
-      </c>
-      <c r="C21" s="26">
-        <f>IF(Monthly!M8=0,0,Monthly!M31/Monthly!M8)</f>
-        <v/>
-      </c>
-      <c r="D21" s="54" t="n"/>
-      <c r="E21" s="55">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D21),D21&gt;=0,D21&lt;=1),D21,C21),C21)</f>
+          <t>Forecast: gateway growth decay (base)</t>
+        </is>
+      </c>
+      <c r="C21" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="48" t="n"/>
+      <c r="E21" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D21),D21&gt;=0,D21&lt;=2),D21,C21),C21)</f>
         <v/>
       </c>
       <c r="F21" s="3">
-        <f>IFERROR(IF(ISBLANK(D21),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D21),"Ignored: error value",IF(NOT(ISNUMBER(D21)),"Ignored: not a number",IF(OR(D21&lt;0,D21&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D21),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D21),"Ignored: error value",IF(NOT(ISNUMBER(D21)),"Ignored: not a number",IF(OR(D21&lt;0,D21&gt;2),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>0 to 2</t>
         </is>
       </c>
       <c r="H21" s="18" t="n"/>
@@ -10235,30 +10233,29 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>price.list</t>
+          <t>ent_ramp_days</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Forecast: list $ per M tokens for pipeline deals</t>
-        </is>
-      </c>
-      <c r="C22" s="26">
-        <f>Data_Params!$B$4</f>
-        <v/>
-      </c>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="55">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D22),D22&gt;=0,D22&lt;=1),D22,C22),C22)</f>
+          <t>Forecast: enterprise ramp length (days)</t>
+        </is>
+      </c>
+      <c r="C22" s="52" t="n">
+        <v>60</v>
+      </c>
+      <c r="D22" s="53" t="n"/>
+      <c r="E22" s="44">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D22),D22&gt;=1,D22&lt;=365),D22,C22),C22)</f>
         <v/>
       </c>
       <c r="F22" s="3">
-        <f>IFERROR(IF(ISBLANK(D22),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D22),"Ignored: error value",IF(NOT(ISNUMBER(D22)),"Ignored: not a number",IF(OR(D22&lt;0,D22&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D22),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D22),"Ignored: error value",IF(NOT(ISNUMBER(D22)),"Ignored: not a number",IF(OR(D22&lt;1,D22&gt;365),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>0 to 1</t>
+          <t>1 to 365</t>
         </is>
       </c>
       <c r="H22" s="18" t="n"/>
@@ -10266,29 +10263,30 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>capacity.gpu_tokens_per_sec</t>
+          <t>price.self_serve</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Capacity: Tokens per second per busy GPU</t>
-        </is>
-      </c>
-      <c r="C23" s="52" t="n">
-        <v>20604</v>
-      </c>
-      <c r="D23" s="53" t="n"/>
-      <c r="E23" s="44">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D23),D23&gt;=1,D23&lt;=10000000),D23,C23),C23)</f>
+          <t>Forecast: self-serve net $ per M tokens (price-change test)</t>
+        </is>
+      </c>
+      <c r="C23" s="26">
+        <f>IF(Monthly!M7=0,0,Monthly!M30/Monthly!M7)</f>
+        <v/>
+      </c>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="55">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D23),D23&gt;=0,D23&lt;=1),D23,C23),C23)</f>
         <v/>
       </c>
       <c r="F23" s="3">
-        <f>IFERROR(IF(ISBLANK(D23),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D23),"Ignored: error value",IF(NOT(ISNUMBER(D23)),"Ignored: not a number",IF(OR(D23&lt;1,D23&gt;10000000),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D23),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D23),"Ignored: error value",IF(NOT(ISNUMBER(D23)),"Ignored: not a number",IF(OR(D23&lt;0,D23&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>1 to 1e+07</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="H23" s="18" t="n"/>
@@ -10296,29 +10294,30 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>capacity.peak_utilization</t>
+          <t>price.gateway</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Capacity: Target utilization at peak</t>
-        </is>
-      </c>
-      <c r="C24" s="50" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D24" s="51" t="n"/>
-      <c r="E24" s="27">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D24),D24&gt;=0.05,D24&lt;=1),D24,C24),C24)</f>
+          <t>Forecast: gateway net $ per M tokens (price-change test)</t>
+        </is>
+      </c>
+      <c r="C24" s="26">
+        <f>IF(Monthly!M8=0,0,Monthly!M31/Monthly!M8)</f>
+        <v/>
+      </c>
+      <c r="D24" s="54" t="n"/>
+      <c r="E24" s="55">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D24),D24&gt;=0,D24&lt;=1),D24,C24),C24)</f>
         <v/>
       </c>
       <c r="F24" s="3">
-        <f>IFERROR(IF(ISBLANK(D24),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D24),"Ignored: error value",IF(NOT(ISNUMBER(D24)),"Ignored: not a number",IF(OR(D24&lt;0.05,D24&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D24),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D24),"Ignored: error value",IF(NOT(ISNUMBER(D24)),"Ignored: not a number",IF(OR(D24&lt;0,D24&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>0.05 to 1</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="H24" s="18" t="n"/>
@@ -10326,29 +10325,30 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>capacity.reserved_rate</t>
+          <t>price.list</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Capacity: Reserved rate ($ / GPU-hour)</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D25" s="57" t="n"/>
-      <c r="E25" s="58">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D25),D25&gt;=0,D25&lt;=100),D25,C25),C25)</f>
+          <t>Forecast: list $ per M tokens for pipeline deals</t>
+        </is>
+      </c>
+      <c r="C25" s="26">
+        <f>Data_Params!$B$4</f>
+        <v/>
+      </c>
+      <c r="D25" s="54" t="n"/>
+      <c r="E25" s="55">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D25),D25&gt;=0,D25&lt;=1),D25,C25),C25)</f>
         <v/>
       </c>
       <c r="F25" s="3">
-        <f>IFERROR(IF(ISBLANK(D25),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D25),"Ignored: error value",IF(NOT(ISNUMBER(D25)),"Ignored: not a number",IF(OR(D25&lt;0,D25&gt;100),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D25),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D25),"Ignored: error value",IF(NOT(ISNUMBER(D25)),"Ignored: not a number",IF(OR(D25&lt;0,D25&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>0 to 100</t>
+          <t>0 to 1</t>
         </is>
       </c>
       <c r="H25" s="18" t="n"/>
@@ -10356,29 +10356,29 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>capacity.on_demand_rate</t>
+          <t>capacity.gpu_tokens_per_sec</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Capacity: On-demand rate ($ / GPU-hour)</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="57" t="n"/>
-      <c r="E26" s="58">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D26),D26&gt;=0,D26&lt;=100),D26,C26),C26)</f>
+          <t>Capacity: Tokens per second per busy GPU</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="n">
+        <v>20604</v>
+      </c>
+      <c r="D26" s="53" t="n"/>
+      <c r="E26" s="44">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D26),D26&gt;=1,D26&lt;=10000000),D26,C26),C26)</f>
         <v/>
       </c>
       <c r="F26" s="3">
-        <f>IFERROR(IF(ISBLANK(D26),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D26),"Ignored: error value",IF(NOT(ISNUMBER(D26)),"Ignored: not a number",IF(OR(D26&lt;0,D26&gt;100),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D26),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D26),"Ignored: error value",IF(NOT(ISNUMBER(D26)),"Ignored: not a number",IF(OR(D26&lt;1,D26&gt;10000000),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>0 to 100</t>
+          <t>1 to 1e+07</t>
         </is>
       </c>
       <c r="H26" s="18" t="n"/>
@@ -10386,29 +10386,29 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>capacity.peak_ratio_override</t>
+          <t>capacity.peak_utilization</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Capacity: Peak hour / average (override if no hourly data)</t>
-        </is>
-      </c>
-      <c r="C27" s="47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="D27" s="48" t="n"/>
-      <c r="E27" s="49">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D27),D27&gt;=1,D27&lt;=20),D27,C27),C27)</f>
+          <t>Capacity: Target utilization at peak</t>
+        </is>
+      </c>
+      <c r="C27" s="50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D27" s="51" t="n"/>
+      <c r="E27" s="27">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D27),D27&gt;=0.05,D27&lt;=1),D27,C27),C27)</f>
         <v/>
       </c>
       <c r="F27" s="3">
-        <f>IFERROR(IF(ISBLANK(D27),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D27),"Ignored: error value",IF(NOT(ISNUMBER(D27)),"Ignored: not a number",IF(OR(D27&lt;1,D27&gt;20),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <f>IFERROR(IF(ISBLANK(D27),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D27),"Ignored: error value",IF(NOT(ISNUMBER(D27)),"Ignored: not a number",IF(OR(D27&lt;0.05,D27&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
         <v/>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>1 to 20</t>
+          <t>0.05 to 1</t>
         </is>
       </c>
       <c r="H27" s="18" t="n"/>
@@ -10416,32 +10416,122 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>capacity.reserved_rate</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Reserved rate ($ / GPU-hour)</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D28" s="57" t="n"/>
+      <c r="E28" s="58">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D28),D28&gt;=0,D28&lt;=100),D28,C28),C28)</f>
+        <v/>
+      </c>
+      <c r="F28" s="3">
+        <f>IFERROR(IF(ISBLANK(D28),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D28),"Ignored: error value",IF(NOT(ISNUMBER(D28)),"Ignored: not a number",IF(OR(D28&lt;0,D28&gt;100),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>0 to 100</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>capacity.on_demand_rate</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: On-demand rate ($ / GPU-hour)</t>
+        </is>
+      </c>
+      <c r="C29" s="56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="58">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D29),D29&gt;=0,D29&lt;=100),D29,C29),C29)</f>
+        <v/>
+      </c>
+      <c r="F29" s="3">
+        <f>IFERROR(IF(ISBLANK(D29),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D29),"Ignored: error value",IF(NOT(ISNUMBER(D29)),"Ignored: not a number",IF(OR(D29&lt;0,D29&gt;100),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>0 to 100</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>capacity.peak_ratio_override</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Capacity: Peak hour / average (override if no hourly data)</t>
+        </is>
+      </c>
+      <c r="C30" s="47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D30" s="48" t="n"/>
+      <c r="E30" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D30),D30&gt;=1,D30&lt;=20),D30,C30),C30)</f>
+        <v/>
+      </c>
+      <c r="F30" s="3">
+        <f>IFERROR(IF(ISBLANK(D30),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D30),"Ignored: error value",IF(NOT(ISNUMBER(D30)),"Ignored: not a number",IF(OR(D30&lt;1,D30&gt;20),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>1 to 20</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>capacity.base_ratio_override</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Capacity: Quietest hour / average (override if no hourly data)</t>
         </is>
       </c>
-      <c r="C28" s="47" t="n">
+      <c r="C31" s="47" t="n">
         <v>0.55</v>
       </c>
-      <c r="D28" s="48" t="n"/>
-      <c r="E28" s="49">
-        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D28),D28&gt;=0,D28&lt;=1),D28,C28),C28)</f>
-        <v/>
-      </c>
-      <c r="F28" s="3">
-        <f>IFERROR(IF(ISBLANK(D28),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D28),"Ignored: error value",IF(NOT(ISNUMBER(D28)),"Ignored: not a number",IF(OR(D28&lt;0,D28&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
-        <v/>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="D31" s="48" t="n"/>
+      <c r="E31" s="49">
+        <f>IFERROR(IF(AND(Overrides!$C$4="ON",ISNUMBER(D31),D31&gt;=0,D31&lt;=1),D31,C31),C31)</f>
+        <v/>
+      </c>
+      <c r="F31" s="3">
+        <f>IFERROR(IF(ISBLANK(D31),"",IF(Overrides!$C$4&lt;&gt;"ON","Switch OFF",IF(ISERROR(D31),"Ignored: error value",IF(NOT(ISNUMBER(D31)),"Ignored: not a number",IF(OR(D31&lt;0,D31&gt;1),"Ignored: outside range","Applied"))))),"Ignored: error value")</f>
+        <v/>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>0 to 1</t>
         </is>
       </c>
-      <c r="H28" s="18" t="n"/>
+      <c r="H31" s="18" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -11083,7 +11173,7 @@
       <formula>$C$4="ON"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="25">
+  <dataValidations count="28">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="ON or OFF" error="Choose ON or OFF." type="list">
       <formula1>"ON,OFF"</formula1>
     </dataValidation>
@@ -11134,51 +11224,63 @@
       <formula1>-0.5</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from -0.5 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 0.5, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.5</formula2>
+    </dataValidation>
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 0.5, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.5</formula2>
+    </dataValidation>
+    <dataValidation sqref="D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 0.5, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>0.5</formula2>
+    </dataValidation>
+    <dataValidation sqref="D20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from -0.5 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>-0.5</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 2, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 2, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation sqref="D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 365, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 365, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>365</formula2>
     </dataValidation>
-    <dataValidation sqref="D20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="D21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="D22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="D23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 1e+07, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 1e+07, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>10000000</formula2>
     </dataValidation>
-    <dataValidation sqref="D24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0.05 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0.05 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0.05</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="D25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 100, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 100, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="D26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 100, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 100, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="D27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 20, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 1 to 20, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation sqref="D28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="D31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Outside the allowed range" error="Enter a number from 0 to 1, or leave blank to use the model value." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -29045,7 +29147,7 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>Overrides!$E$17</f>
+        <f>Overrides!$E$20</f>
         <v/>
       </c>
       <c r="C7" s="25">
@@ -29117,7 +29219,7 @@
         </is>
       </c>
       <c r="C10" s="35">
-        <f>Overrides!$E$18</f>
+        <f>Overrides!$E$21</f>
         <v/>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -29177,7 +29279,7 @@
         </is>
       </c>
       <c r="C13" s="12">
-        <f>Overrides!$E$19</f>
+        <f>Overrides!$E$22</f>
         <v/>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -29193,7 +29295,7 @@
         </is>
       </c>
       <c r="C14" s="13">
-        <f>Overrides!$E$20</f>
+        <f>Overrides!$E$23</f>
         <v/>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -29209,7 +29311,7 @@
         </is>
       </c>
       <c r="C15" s="13">
-        <f>Overrides!$E$21</f>
+        <f>Overrides!$E$24</f>
         <v/>
       </c>
       <c r="E15" s="7" t="inlineStr"/>
@@ -29230,7 +29332,30 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Self-serve tokens lost to competitors, per month</t>
+        </is>
+      </c>
+      <c r="B17" s="11">
+        <f>Overrides!$E$17</f>
+        <v/>
+      </c>
+      <c r="C17" s="37">
+        <f>Overrides!$E$18</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>Overrides!$E$19</f>
+        <v/>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Rival decision APIs (OpenAI Decisions API, AWS Strands Decider). Compounds monthly.</t>
+        </is>
+      </c>
+    </row>
     <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -32603,15 +32728,15 @@
         </is>
       </c>
       <c r="B111" s="24">
-        <f>SUM(P51,O52,N53,M54,L55,K56,J57,I58,H59,G60,F61,E62,D63)+$C$16*$B$6^1</f>
+        <f>(SUM(P51,O52,N53,M54,L55,K56,J57,I58,H59,G60,F61,E62,D63)+$C$16*$B$6^1)*(1-$B$17)^1</f>
         <v/>
       </c>
       <c r="C111" s="24">
-        <f>SUM(Q51,P52,O53,N54,M55,L56,K57,J58,I59,H60,G61,F62,E63,D64)+$C$16*$B$6^2</f>
+        <f>(SUM(Q51,P52,O53,N54,M55,L56,K57,J58,I59,H60,G61,F62,E63,D64)+$C$16*$B$6^2)*(1-$B$17)^2</f>
         <v/>
       </c>
       <c r="D111" s="24">
-        <f>SUM(R51,Q52,P53,O54,N55,M56,L57,K58,J59,I60,H61,G62,F63,E64,D65)+$C$16*$B$6^3</f>
+        <f>(SUM(R51,Q52,P53,O54,N55,M56,L57,K58,J59,I60,H61,G62,F63,E64,D65)+$C$16*$B$6^3)*(1-$B$17)^3</f>
         <v/>
       </c>
     </row>
@@ -32622,15 +32747,15 @@
         </is>
       </c>
       <c r="B112" s="24">
-        <f>SUM(P71,O72,N73,M74,L75,K76,J77,I78,H79,G80,F81,E82,D83)+$C$16*$C$6^1</f>
+        <f>(SUM(P71,O72,N73,M74,L75,K76,J77,I78,H79,G80,F81,E82,D83)+$C$16*$C$6^1)*(1-$C$17)^1</f>
         <v/>
       </c>
       <c r="C112" s="24">
-        <f>SUM(Q71,P72,O73,N74,M75,L76,K77,J78,I79,H80,G81,F82,E83,D84)+$C$16*$C$6^2</f>
+        <f>(SUM(Q71,P72,O73,N74,M75,L76,K77,J78,I79,H80,G81,F82,E83,D84)+$C$16*$C$6^2)*(1-$C$17)^2</f>
         <v/>
       </c>
       <c r="D112" s="24">
-        <f>SUM(R71,Q72,P73,O74,N75,M76,L77,K78,J79,I80,H81,G82,F83,E84,D85)+$C$16*$C$6^3</f>
+        <f>(SUM(R71,Q72,P73,O74,N75,M76,L77,K78,J79,I80,H81,G82,F83,E84,D85)+$C$16*$C$6^3)*(1-$C$17)^3</f>
         <v/>
       </c>
     </row>
@@ -32641,15 +32766,15 @@
         </is>
       </c>
       <c r="B113" s="24">
-        <f>SUM(P91,O92,N93,M94,L95,K96,J97,I98,H99,G100,F101,E102,D103)+$C$16*$D$6^1</f>
+        <f>(SUM(P91,O92,N93,M94,L95,K96,J97,I98,H99,G100,F101,E102,D103)+$C$16*$D$6^1)*(1-$D$17)^1</f>
         <v/>
       </c>
       <c r="C113" s="24">
-        <f>SUM(Q91,P92,O93,N94,M95,L96,K97,J98,I99,H100,G101,F102,E103,D104)+$C$16*$D$6^2</f>
+        <f>(SUM(Q91,P92,O93,N94,M95,L96,K97,J98,I99,H100,G101,F102,E103,D104)+$C$16*$D$6^2)*(1-$D$17)^2</f>
         <v/>
       </c>
       <c r="D113" s="24">
-        <f>SUM(R91,Q92,P93,O94,N95,M96,L97,K98,J99,I100,H101,G102,F103,E104,D105)+$C$16*$D$6^3</f>
+        <f>(SUM(R91,Q92,P93,O94,N95,M96,L97,K98,J99,I100,H101,G102,F103,E104,D105)+$C$16*$D$6^3)*(1-$D$17)^3</f>
         <v/>
       </c>
     </row>
